--- a/maliyetler.xlsx
+++ b/maliyetler.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Desktop\geminitrendyol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A482F2C-9E29-41C7-A937-9681561D1D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86FE5F2-01D0-4BC9-84C2-F011BE524812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$D$263</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="315">
   <si>
     <t>Barkod</t>
   </si>
@@ -787,6 +798,192 @@
   </si>
   <si>
     <t>0.215</t>
+  </si>
+  <si>
+    <t>dRKD-0326</t>
+  </si>
+  <si>
+    <t>dRKD-0325</t>
+  </si>
+  <si>
+    <t>dRKD-0324</t>
+  </si>
+  <si>
+    <t>dRKD-0322</t>
+  </si>
+  <si>
+    <t>dRKD-0323</t>
+  </si>
+  <si>
+    <t>dRKD-0319</t>
+  </si>
+  <si>
+    <t>dRKD-0317</t>
+  </si>
+  <si>
+    <t>dRKD-0321</t>
+  </si>
+  <si>
+    <t>dRKD-0318</t>
+  </si>
+  <si>
+    <t>dRKD-0320</t>
+  </si>
+  <si>
+    <t>dRKD-0218</t>
+  </si>
+  <si>
+    <t>dRKD-0219</t>
+  </si>
+  <si>
+    <t>dRKD-0222</t>
+  </si>
+  <si>
+    <t>dRKD-0221</t>
+  </si>
+  <si>
+    <t>dRKD-0217</t>
+  </si>
+  <si>
+    <t>dRKD-0216</t>
+  </si>
+  <si>
+    <t>dRKD-0212</t>
+  </si>
+  <si>
+    <t>dRKD-0213</t>
+  </si>
+  <si>
+    <t>dRKD-0215</t>
+  </si>
+  <si>
+    <t>dRKD-0214</t>
+  </si>
+  <si>
+    <t>dRKD-0211</t>
+  </si>
+  <si>
+    <t>dRKD-0204</t>
+  </si>
+  <si>
+    <t>dRKD-0200</t>
+  </si>
+  <si>
+    <t>dRKD-0199</t>
+  </si>
+  <si>
+    <t>dRKD-0201</t>
+  </si>
+  <si>
+    <t>dRKD-0202</t>
+  </si>
+  <si>
+    <t>dRKD-0203</t>
+  </si>
+  <si>
+    <t>dRKD-0210</t>
+  </si>
+  <si>
+    <t>dRKD-0209</t>
+  </si>
+  <si>
+    <t>dRKD-0208</t>
+  </si>
+  <si>
+    <t>dRKD-0207</t>
+  </si>
+  <si>
+    <t>dRKD-0206</t>
+  </si>
+  <si>
+    <t>dRKD-0205</t>
+  </si>
+  <si>
+    <t>dRKD-0236</t>
+  </si>
+  <si>
+    <t>dRKD-0234</t>
+  </si>
+  <si>
+    <t>dRKD-0235</t>
+  </si>
+  <si>
+    <t>dRKD-0233</t>
+  </si>
+  <si>
+    <t>dRKD-0237</t>
+  </si>
+  <si>
+    <t>dRKD-0239</t>
+  </si>
+  <si>
+    <t>dRKD-0242</t>
+  </si>
+  <si>
+    <t>dRKD-0241</t>
+  </si>
+  <si>
+    <t>dRKD-0240</t>
+  </si>
+  <si>
+    <t>dRKD-0238</t>
+  </si>
+  <si>
+    <t>dRKD-0247</t>
+  </si>
+  <si>
+    <t>dRKD-0246</t>
+  </si>
+  <si>
+    <t>dRKD-0244</t>
+  </si>
+  <si>
+    <t>dRKD-0243</t>
+  </si>
+  <si>
+    <t>dRKD-0245</t>
+  </si>
+  <si>
+    <t>dRKD-0251</t>
+  </si>
+  <si>
+    <t>dRKD-0252</t>
+  </si>
+  <si>
+    <t>dRKD-0249</t>
+  </si>
+  <si>
+    <t>dRKD-0248</t>
+  </si>
+  <si>
+    <t>dRKD-0250</t>
+  </si>
+  <si>
+    <t>dRKD-0228</t>
+  </si>
+  <si>
+    <t>dRKD-0230</t>
+  </si>
+  <si>
+    <t>dRKD-0229</t>
+  </si>
+  <si>
+    <t>dRKD-0231</t>
+  </si>
+  <si>
+    <t>dRKD-0226</t>
+  </si>
+  <si>
+    <t>dRKD-0223</t>
+  </si>
+  <si>
+    <t>dRKD-0225</t>
+  </si>
+  <si>
+    <t>dRKD-0224</t>
+  </si>
+  <si>
+    <t>dRKD-0227</t>
   </si>
 </sst>
 </file>
@@ -1110,13 +1307,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D263"/>
+  <dimension ref="A1:D325"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -4801,6 +5000,874 @@
         <v>252</v>
       </c>
     </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>253</v>
+      </c>
+      <c r="B264">
+        <v>100</v>
+      </c>
+      <c r="C264">
+        <v>100</v>
+      </c>
+      <c r="D264" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>254</v>
+      </c>
+      <c r="B265">
+        <v>100</v>
+      </c>
+      <c r="C265">
+        <v>100</v>
+      </c>
+      <c r="D265" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>255</v>
+      </c>
+      <c r="B266">
+        <v>100</v>
+      </c>
+      <c r="C266">
+        <v>100</v>
+      </c>
+      <c r="D266" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>256</v>
+      </c>
+      <c r="B267">
+        <v>100</v>
+      </c>
+      <c r="C267">
+        <v>100</v>
+      </c>
+      <c r="D267" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>257</v>
+      </c>
+      <c r="B268">
+        <v>100</v>
+      </c>
+      <c r="C268">
+        <v>100</v>
+      </c>
+      <c r="D268" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>258</v>
+      </c>
+      <c r="B269">
+        <v>100</v>
+      </c>
+      <c r="C269">
+        <v>100</v>
+      </c>
+      <c r="D269" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>259</v>
+      </c>
+      <c r="B270">
+        <v>100</v>
+      </c>
+      <c r="C270">
+        <v>100</v>
+      </c>
+      <c r="D270" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>260</v>
+      </c>
+      <c r="B271">
+        <v>100</v>
+      </c>
+      <c r="C271">
+        <v>100</v>
+      </c>
+      <c r="D271" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>261</v>
+      </c>
+      <c r="B272">
+        <v>100</v>
+      </c>
+      <c r="C272">
+        <v>100</v>
+      </c>
+      <c r="D272" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>262</v>
+      </c>
+      <c r="B273">
+        <v>100</v>
+      </c>
+      <c r="C273">
+        <v>100</v>
+      </c>
+      <c r="D273" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>263</v>
+      </c>
+      <c r="B274">
+        <v>100</v>
+      </c>
+      <c r="C274">
+        <v>100</v>
+      </c>
+      <c r="D274" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>264</v>
+      </c>
+      <c r="B275">
+        <v>100</v>
+      </c>
+      <c r="C275">
+        <v>100</v>
+      </c>
+      <c r="D275" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>265</v>
+      </c>
+      <c r="B276">
+        <v>100</v>
+      </c>
+      <c r="C276">
+        <v>100</v>
+      </c>
+      <c r="D276" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>266</v>
+      </c>
+      <c r="B277">
+        <v>100</v>
+      </c>
+      <c r="C277">
+        <v>100</v>
+      </c>
+      <c r="D277" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>267</v>
+      </c>
+      <c r="B278">
+        <v>100</v>
+      </c>
+      <c r="C278">
+        <v>100</v>
+      </c>
+      <c r="D278" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>268</v>
+      </c>
+      <c r="B279">
+        <v>100</v>
+      </c>
+      <c r="C279">
+        <v>100</v>
+      </c>
+      <c r="D279" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>269</v>
+      </c>
+      <c r="B280">
+        <v>100</v>
+      </c>
+      <c r="C280">
+        <v>100</v>
+      </c>
+      <c r="D280" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>270</v>
+      </c>
+      <c r="B281">
+        <v>100</v>
+      </c>
+      <c r="C281">
+        <v>100</v>
+      </c>
+      <c r="D281" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>271</v>
+      </c>
+      <c r="B282">
+        <v>100</v>
+      </c>
+      <c r="C282">
+        <v>100</v>
+      </c>
+      <c r="D282" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>272</v>
+      </c>
+      <c r="B283">
+        <v>100</v>
+      </c>
+      <c r="C283">
+        <v>100</v>
+      </c>
+      <c r="D283" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>273</v>
+      </c>
+      <c r="B284">
+        <v>100</v>
+      </c>
+      <c r="C284">
+        <v>100</v>
+      </c>
+      <c r="D284" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>274</v>
+      </c>
+      <c r="B285">
+        <v>100</v>
+      </c>
+      <c r="C285">
+        <v>100</v>
+      </c>
+      <c r="D285" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>275</v>
+      </c>
+      <c r="B286">
+        <v>100</v>
+      </c>
+      <c r="C286">
+        <v>100</v>
+      </c>
+      <c r="D286" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>276</v>
+      </c>
+      <c r="B287">
+        <v>100</v>
+      </c>
+      <c r="C287">
+        <v>100</v>
+      </c>
+      <c r="D287" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>277</v>
+      </c>
+      <c r="B288">
+        <v>100</v>
+      </c>
+      <c r="C288">
+        <v>100</v>
+      </c>
+      <c r="D288" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>278</v>
+      </c>
+      <c r="B289">
+        <v>100</v>
+      </c>
+      <c r="C289">
+        <v>100</v>
+      </c>
+      <c r="D289" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>279</v>
+      </c>
+      <c r="B290">
+        <v>100</v>
+      </c>
+      <c r="C290">
+        <v>100</v>
+      </c>
+      <c r="D290" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>280</v>
+      </c>
+      <c r="B291">
+        <v>100</v>
+      </c>
+      <c r="C291">
+        <v>100</v>
+      </c>
+      <c r="D291" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>281</v>
+      </c>
+      <c r="B292">
+        <v>100</v>
+      </c>
+      <c r="C292">
+        <v>100</v>
+      </c>
+      <c r="D292" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>282</v>
+      </c>
+      <c r="B293">
+        <v>100</v>
+      </c>
+      <c r="C293">
+        <v>100</v>
+      </c>
+      <c r="D293" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>283</v>
+      </c>
+      <c r="B294">
+        <v>100</v>
+      </c>
+      <c r="C294">
+        <v>100</v>
+      </c>
+      <c r="D294" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>284</v>
+      </c>
+      <c r="B295">
+        <v>100</v>
+      </c>
+      <c r="C295">
+        <v>100</v>
+      </c>
+      <c r="D295" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>285</v>
+      </c>
+      <c r="B296">
+        <v>100</v>
+      </c>
+      <c r="C296">
+        <v>100</v>
+      </c>
+      <c r="D296" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>286</v>
+      </c>
+      <c r="B297">
+        <v>175</v>
+      </c>
+      <c r="C297">
+        <v>100</v>
+      </c>
+      <c r="D297" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>287</v>
+      </c>
+      <c r="B298">
+        <v>175</v>
+      </c>
+      <c r="C298">
+        <v>100</v>
+      </c>
+      <c r="D298" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>288</v>
+      </c>
+      <c r="B299">
+        <v>175</v>
+      </c>
+      <c r="C299">
+        <v>100</v>
+      </c>
+      <c r="D299" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>289</v>
+      </c>
+      <c r="B300">
+        <v>175</v>
+      </c>
+      <c r="C300">
+        <v>100</v>
+      </c>
+      <c r="D300" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>290</v>
+      </c>
+      <c r="B301">
+        <v>175</v>
+      </c>
+      <c r="C301">
+        <v>100</v>
+      </c>
+      <c r="D301" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>291</v>
+      </c>
+      <c r="B302">
+        <v>175</v>
+      </c>
+      <c r="C302">
+        <v>100</v>
+      </c>
+      <c r="D302" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>292</v>
+      </c>
+      <c r="B303">
+        <v>175</v>
+      </c>
+      <c r="C303">
+        <v>100</v>
+      </c>
+      <c r="D303" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>293</v>
+      </c>
+      <c r="B304">
+        <v>175</v>
+      </c>
+      <c r="C304">
+        <v>100</v>
+      </c>
+      <c r="D304" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>294</v>
+      </c>
+      <c r="B305">
+        <v>175</v>
+      </c>
+      <c r="C305">
+        <v>100</v>
+      </c>
+      <c r="D305" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>295</v>
+      </c>
+      <c r="B306">
+        <v>175</v>
+      </c>
+      <c r="C306">
+        <v>100</v>
+      </c>
+      <c r="D306" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>296</v>
+      </c>
+      <c r="B307">
+        <v>150</v>
+      </c>
+      <c r="C307">
+        <v>100</v>
+      </c>
+      <c r="D307" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>297</v>
+      </c>
+      <c r="B308">
+        <v>150</v>
+      </c>
+      <c r="C308">
+        <v>100</v>
+      </c>
+      <c r="D308" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>298</v>
+      </c>
+      <c r="B309">
+        <v>150</v>
+      </c>
+      <c r="C309">
+        <v>100</v>
+      </c>
+      <c r="D309" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>299</v>
+      </c>
+      <c r="B310">
+        <v>150</v>
+      </c>
+      <c r="C310">
+        <v>100</v>
+      </c>
+      <c r="D310" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>300</v>
+      </c>
+      <c r="B311">
+        <v>150</v>
+      </c>
+      <c r="C311">
+        <v>100</v>
+      </c>
+      <c r="D311" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>301</v>
+      </c>
+      <c r="B312">
+        <v>150</v>
+      </c>
+      <c r="C312">
+        <v>100</v>
+      </c>
+      <c r="D312" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>302</v>
+      </c>
+      <c r="B313">
+        <v>150</v>
+      </c>
+      <c r="C313">
+        <v>100</v>
+      </c>
+      <c r="D313" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>303</v>
+      </c>
+      <c r="B314">
+        <v>150</v>
+      </c>
+      <c r="C314">
+        <v>100</v>
+      </c>
+      <c r="D314" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>304</v>
+      </c>
+      <c r="B315">
+        <v>150</v>
+      </c>
+      <c r="C315">
+        <v>100</v>
+      </c>
+      <c r="D315" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>305</v>
+      </c>
+      <c r="B316">
+        <v>150</v>
+      </c>
+      <c r="C316">
+        <v>100</v>
+      </c>
+      <c r="D316" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>306</v>
+      </c>
+      <c r="B317">
+        <v>225</v>
+      </c>
+      <c r="C317">
+        <v>100</v>
+      </c>
+      <c r="D317" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>307</v>
+      </c>
+      <c r="B318">
+        <v>225</v>
+      </c>
+      <c r="C318">
+        <v>100</v>
+      </c>
+      <c r="D318" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>308</v>
+      </c>
+      <c r="B319">
+        <v>225</v>
+      </c>
+      <c r="C319">
+        <v>100</v>
+      </c>
+      <c r="D319" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>309</v>
+      </c>
+      <c r="B320">
+        <v>225</v>
+      </c>
+      <c r="C320">
+        <v>100</v>
+      </c>
+      <c r="D320" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>310</v>
+      </c>
+      <c r="B321">
+        <v>225</v>
+      </c>
+      <c r="C321">
+        <v>100</v>
+      </c>
+      <c r="D321" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>311</v>
+      </c>
+      <c r="B322">
+        <v>225</v>
+      </c>
+      <c r="C322">
+        <v>100</v>
+      </c>
+      <c r="D322" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>312</v>
+      </c>
+      <c r="B323">
+        <v>225</v>
+      </c>
+      <c r="C323">
+        <v>100</v>
+      </c>
+      <c r="D323" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>313</v>
+      </c>
+      <c r="B324">
+        <v>225</v>
+      </c>
+      <c r="C324">
+        <v>100</v>
+      </c>
+      <c r="D324" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>314</v>
+      </c>
+      <c r="B325">
+        <v>225</v>
+      </c>
+      <c r="C325">
+        <v>100</v>
+      </c>
+      <c r="D325" t="s">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/maliyetler.xlsx
+++ b/maliyetler.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86FE5F2-01D0-4BC9-84C2-F011BE524812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FA63D2-74F4-4168-9B4B-9CDC8E5BA35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="461">
   <si>
     <t>Barkod</t>
   </si>
@@ -984,6 +984,444 @@
   </si>
   <si>
     <t>dRKD-0227</t>
+  </si>
+  <si>
+    <t>dRKD-0001</t>
+  </si>
+  <si>
+    <t>dRKD-0002</t>
+  </si>
+  <si>
+    <t>dRKD-0003</t>
+  </si>
+  <si>
+    <t>dRKD-0004</t>
+  </si>
+  <si>
+    <t>dRKD-0005</t>
+  </si>
+  <si>
+    <t>dRKD-0006</t>
+  </si>
+  <si>
+    <t>dRKD-0007</t>
+  </si>
+  <si>
+    <t>dRKD-0008</t>
+  </si>
+  <si>
+    <t>dRKD-0009</t>
+  </si>
+  <si>
+    <t>dRKD-0010</t>
+  </si>
+  <si>
+    <t>dRKD-0408</t>
+  </si>
+  <si>
+    <t>dRKD-0410</t>
+  </si>
+  <si>
+    <t>dRKD-0409</t>
+  </si>
+  <si>
+    <t>dRKD-0407</t>
+  </si>
+  <si>
+    <t>dRKD-0431</t>
+  </si>
+  <si>
+    <t>dRKD-0434</t>
+  </si>
+  <si>
+    <t>dRKD-0432</t>
+  </si>
+  <si>
+    <t>dRKD-0433</t>
+  </si>
+  <si>
+    <t>dRKD-0393</t>
+  </si>
+  <si>
+    <t>dRKD-0391</t>
+  </si>
+  <si>
+    <t>dRKD-0392</t>
+  </si>
+  <si>
+    <t>dRKD-0394</t>
+  </si>
+  <si>
+    <t>dRKD-0440</t>
+  </si>
+  <si>
+    <t>dRKD-0441</t>
+  </si>
+  <si>
+    <t>dRKD-0442</t>
+  </si>
+  <si>
+    <t>dRKD-0439</t>
+  </si>
+  <si>
+    <t>dRKD-0448</t>
+  </si>
+  <si>
+    <t>dRKD-0449</t>
+  </si>
+  <si>
+    <t>dRKD-0450</t>
+  </si>
+  <si>
+    <t>dRKD-0447</t>
+  </si>
+  <si>
+    <t>dRKD-0396</t>
+  </si>
+  <si>
+    <t>dRKD-0397</t>
+  </si>
+  <si>
+    <t>dRKD-0398</t>
+  </si>
+  <si>
+    <t>dRKD-0395</t>
+  </si>
+  <si>
+    <t>dRKD-0400</t>
+  </si>
+  <si>
+    <t>dRKD-0401</t>
+  </si>
+  <si>
+    <t>dRKD-0402</t>
+  </si>
+  <si>
+    <t>dRKD-0399</t>
+  </si>
+  <si>
+    <t>dRKD-0453</t>
+  </si>
+  <si>
+    <t>dRKD-0452</t>
+  </si>
+  <si>
+    <t>dRKD-0454</t>
+  </si>
+  <si>
+    <t>dRKD-0451</t>
+  </si>
+  <si>
+    <t>dRKD-0426</t>
+  </si>
+  <si>
+    <t>dRKD-0423</t>
+  </si>
+  <si>
+    <t>dRKD-0424</t>
+  </si>
+  <si>
+    <t>dRKD-0425</t>
+  </si>
+  <si>
+    <t>dRKD-0418</t>
+  </si>
+  <si>
+    <t>dRKD-0417</t>
+  </si>
+  <si>
+    <t>dRKD-0415</t>
+  </si>
+  <si>
+    <t>dRKD-0416</t>
+  </si>
+  <si>
+    <t>dRKD-0428</t>
+  </si>
+  <si>
+    <t>dRKD-0430</t>
+  </si>
+  <si>
+    <t>dRKD-0427</t>
+  </si>
+  <si>
+    <t>dRKD-0429</t>
+  </si>
+  <si>
+    <t>dRKD-0414</t>
+  </si>
+  <si>
+    <t>dRKD-0412</t>
+  </si>
+  <si>
+    <t>dRKD-0411</t>
+  </si>
+  <si>
+    <t>dRKD-0413</t>
+  </si>
+  <si>
+    <t>dRKD-0438</t>
+  </si>
+  <si>
+    <t>dRKD-0435</t>
+  </si>
+  <si>
+    <t>dRKD-0436</t>
+  </si>
+  <si>
+    <t>dRKD-0437</t>
+  </si>
+  <si>
+    <t>dRKD-0446</t>
+  </si>
+  <si>
+    <t>dRKD-0443</t>
+  </si>
+  <si>
+    <t>dRKD-0445</t>
+  </si>
+  <si>
+    <t>dRKD-0444</t>
+  </si>
+  <si>
+    <t>dRKD-0419</t>
+  </si>
+  <si>
+    <t>dRKD-0420</t>
+  </si>
+  <si>
+    <t>dRKD-0421</t>
+  </si>
+  <si>
+    <t>dRKD-0422</t>
+  </si>
+  <si>
+    <t>dRKD-0403</t>
+  </si>
+  <si>
+    <t>dRKD-0406</t>
+  </si>
+  <si>
+    <t>dRKD-0405</t>
+  </si>
+  <si>
+    <t>dRKD-0404</t>
+  </si>
+  <si>
+    <t>dRKD-0378</t>
+  </si>
+  <si>
+    <t>dRKD-0376</t>
+  </si>
+  <si>
+    <t>dRKD-0377</t>
+  </si>
+  <si>
+    <t>dRKD-0375</t>
+  </si>
+  <si>
+    <t>dRKD-0367</t>
+  </si>
+  <si>
+    <t>dRKD-0368</t>
+  </si>
+  <si>
+    <t>dRKD-0369</t>
+  </si>
+  <si>
+    <t>dRKD-0370</t>
+  </si>
+  <si>
+    <t>dRKD-0361</t>
+  </si>
+  <si>
+    <t>dRKD-0360</t>
+  </si>
+  <si>
+    <t>dRKD-0362</t>
+  </si>
+  <si>
+    <t>dRKD-0359</t>
+  </si>
+  <si>
+    <t>dRKD-0363</t>
+  </si>
+  <si>
+    <t>dRKD-0366</t>
+  </si>
+  <si>
+    <t>dRKD-0364</t>
+  </si>
+  <si>
+    <t>dRKD-0365</t>
+  </si>
+  <si>
+    <t>dRKD-0382</t>
+  </si>
+  <si>
+    <t>dRKD-0381</t>
+  </si>
+  <si>
+    <t>dRKD-0379</t>
+  </si>
+  <si>
+    <t>dRKD-0380</t>
+  </si>
+  <si>
+    <t>dRKD-0374</t>
+  </si>
+  <si>
+    <t>dRKD-0372</t>
+  </si>
+  <si>
+    <t>dRKD-0371</t>
+  </si>
+  <si>
+    <t>dRKD-0373</t>
+  </si>
+  <si>
+    <t>dRKD-0339</t>
+  </si>
+  <si>
+    <t>dRKD-0340</t>
+  </si>
+  <si>
+    <t>dRKD-0341</t>
+  </si>
+  <si>
+    <t>dRKD-0342</t>
+  </si>
+  <si>
+    <t>dRKD-0343</t>
+  </si>
+  <si>
+    <t>dRKD-0344</t>
+  </si>
+  <si>
+    <t>dRKD-0345</t>
+  </si>
+  <si>
+    <t>dRKD-0346</t>
+  </si>
+  <si>
+    <t>dRKD-0347</t>
+  </si>
+  <si>
+    <t>dRKD-0348</t>
+  </si>
+  <si>
+    <t>dRKD-0349</t>
+  </si>
+  <si>
+    <t>dRKD-0350</t>
+  </si>
+  <si>
+    <t>dRKD-0351</t>
+  </si>
+  <si>
+    <t>dRKD-0352</t>
+  </si>
+  <si>
+    <t>dRKD-0353</t>
+  </si>
+  <si>
+    <t>dRKD-0354</t>
+  </si>
+  <si>
+    <t>dRKD-0355</t>
+  </si>
+  <si>
+    <t>dRKD-0356</t>
+  </si>
+  <si>
+    <t>dRKD-0357</t>
+  </si>
+  <si>
+    <t>dRKD-0358</t>
+  </si>
+  <si>
+    <t>dRKD-0455</t>
+  </si>
+  <si>
+    <t>dRKD-0456</t>
+  </si>
+  <si>
+    <t>dRKD-0457</t>
+  </si>
+  <si>
+    <t>dRKD-0458</t>
+  </si>
+  <si>
+    <t>dRKD-0463</t>
+  </si>
+  <si>
+    <t>dRKD-0464</t>
+  </si>
+  <si>
+    <t>dRKD-0465</t>
+  </si>
+  <si>
+    <t>dRKD-0466</t>
+  </si>
+  <si>
+    <t>dRKD-0467</t>
+  </si>
+  <si>
+    <t>dRKD-0468</t>
+  </si>
+  <si>
+    <t>dRKD-0469</t>
+  </si>
+  <si>
+    <t>dRKD-0470</t>
+  </si>
+  <si>
+    <t>dRKD-0471</t>
+  </si>
+  <si>
+    <t>dRKD-0472</t>
+  </si>
+  <si>
+    <t>dRKD-0473</t>
+  </si>
+  <si>
+    <t>dRKD-0474</t>
+  </si>
+  <si>
+    <t>dRKD-0475</t>
+  </si>
+  <si>
+    <t>dRKD-0476</t>
+  </si>
+  <si>
+    <t>dRKD-0477</t>
+  </si>
+  <si>
+    <t>dRKD-0478</t>
+  </si>
+  <si>
+    <t>dRKD-0479</t>
+  </si>
+  <si>
+    <t>dRKD-0480</t>
+  </si>
+  <si>
+    <t>dRKD-0481</t>
+  </si>
+  <si>
+    <t>dRKD-0482</t>
+  </si>
+  <si>
+    <t>dRKD-0483</t>
+  </si>
+  <si>
+    <t>dRKD-0484</t>
+  </si>
+  <si>
+    <t>dRKD-0485</t>
+  </si>
+  <si>
+    <t>dRKD-0486</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D457"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -1315,7 +1753,6 @@
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1334,10 +1771,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>315</v>
       </c>
       <c r="B2">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1348,10 +1785,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>316</v>
       </c>
       <c r="B3">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1362,10 +1799,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>317</v>
       </c>
       <c r="B4">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1376,10 +1813,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>318</v>
       </c>
       <c r="B5">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1390,10 +1827,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>319</v>
       </c>
       <c r="B6">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1404,10 +1841,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>320</v>
       </c>
       <c r="B7">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1418,10 +1855,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>321</v>
       </c>
       <c r="B8">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1432,10 +1869,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>322</v>
       </c>
       <c r="B9">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1446,10 +1883,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>323</v>
       </c>
       <c r="B10">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1460,10 +1897,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>324</v>
       </c>
       <c r="B11">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1474,10 +1911,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B12">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1488,10 +1925,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1502,10 +1939,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B14">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1516,10 +1953,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B15">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1530,10 +1967,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1544,10 +1981,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B17">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1558,10 +1995,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -1572,10 +2009,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B19">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1586,10 +2023,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B20">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -1600,10 +2037,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1614,10 +2051,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B22">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1628,10 +2065,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B23">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -1642,10 +2079,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B24">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -1656,10 +2093,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -1670,10 +2107,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -1684,10 +2121,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B27">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -1698,10 +2135,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -1712,10 +2149,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B29">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -1726,10 +2163,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B30">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -1740,10 +2177,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B31">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -1754,10 +2191,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B32">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -1768,10 +2205,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B33">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -1782,10 +2219,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="B34">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -1796,10 +2233,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>326</v>
       </c>
       <c r="B35">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -1810,10 +2247,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
       <c r="B36">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -1824,10 +2261,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>328</v>
       </c>
       <c r="B37">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -1838,10 +2275,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="B38">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -1852,10 +2289,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>330</v>
       </c>
       <c r="B39">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -1866,10 +2303,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>331</v>
       </c>
       <c r="B40">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -1880,10 +2317,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>332</v>
       </c>
       <c r="B41">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -1894,10 +2331,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>333</v>
       </c>
       <c r="B42">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -1908,10 +2345,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="B43">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -1922,10 +2359,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>335</v>
       </c>
       <c r="B44">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -1936,10 +2373,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>336</v>
       </c>
       <c r="B45">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -1950,10 +2387,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>337</v>
       </c>
       <c r="B46">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -1964,10 +2401,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>338</v>
       </c>
       <c r="B47">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -1978,10 +2415,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>339</v>
       </c>
       <c r="B48">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -1992,10 +2429,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>340</v>
       </c>
       <c r="B49">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C49">
         <v>100</v>
@@ -2006,10 +2443,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>341</v>
       </c>
       <c r="B50">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2020,10 +2457,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>342</v>
       </c>
       <c r="B51">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2034,10 +2471,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>343</v>
       </c>
       <c r="B52">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C52">
         <v>100</v>
@@ -2048,10 +2485,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>344</v>
       </c>
       <c r="B53">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c r="C53">
         <v>100</v>
@@ -2062,10 +2499,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>345</v>
       </c>
       <c r="B54">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C54">
         <v>100</v>
@@ -2076,10 +2513,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="B55">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C55">
         <v>100</v>
@@ -2090,10 +2527,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="B56">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C56">
         <v>100</v>
@@ -2104,10 +2541,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>348</v>
       </c>
       <c r="B57">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C57">
         <v>100</v>
@@ -2118,10 +2555,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="B58">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C58">
         <v>100</v>
@@ -2132,10 +2569,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>350</v>
       </c>
       <c r="B59">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C59">
         <v>100</v>
@@ -2146,10 +2583,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>351</v>
       </c>
       <c r="B60">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C60">
         <v>100</v>
@@ -2160,10 +2597,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>352</v>
       </c>
       <c r="B61">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C61">
         <v>100</v>
@@ -2174,10 +2611,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="B62">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C62">
         <v>100</v>
@@ -2188,10 +2625,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>354</v>
       </c>
       <c r="B63">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C63">
         <v>100</v>
@@ -2202,10 +2639,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>355</v>
       </c>
       <c r="B64">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C64">
         <v>100</v>
@@ -2216,10 +2653,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>356</v>
       </c>
       <c r="B65">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C65">
         <v>100</v>
@@ -2230,10 +2667,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>357</v>
       </c>
       <c r="B66">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C66">
         <v>100</v>
@@ -2244,10 +2681,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>358</v>
       </c>
       <c r="B67">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -2258,10 +2695,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>359</v>
       </c>
       <c r="B68">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -2272,10 +2709,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>360</v>
       </c>
       <c r="B69">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C69">
         <v>100</v>
@@ -2286,10 +2723,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="B70">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -2300,10 +2737,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>362</v>
       </c>
       <c r="B71">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C71">
         <v>100</v>
@@ -2314,10 +2751,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="B72">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C72">
         <v>100</v>
@@ -2328,10 +2765,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="B73">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C73">
         <v>100</v>
@@ -2342,10 +2779,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>365</v>
       </c>
       <c r="B74">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C74">
         <v>100</v>
@@ -2356,10 +2793,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="B75">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C75">
         <v>100</v>
@@ -2370,10 +2807,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="B76">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C76">
         <v>100</v>
@@ -2384,10 +2821,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="B77">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C77">
         <v>100</v>
@@ -2398,10 +2835,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="B78">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C78">
         <v>100</v>
@@ -2412,10 +2849,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="B79">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C79">
         <v>100</v>
@@ -2426,10 +2863,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="B80">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C80">
         <v>100</v>
@@ -2440,10 +2877,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="B81">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C81">
         <v>100</v>
@@ -2454,10 +2891,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>373</v>
       </c>
       <c r="B82">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C82">
         <v>100</v>
@@ -2468,10 +2905,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>374</v>
       </c>
       <c r="B83">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C83">
         <v>100</v>
@@ -2482,10 +2919,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>375</v>
       </c>
       <c r="B84">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C84">
         <v>100</v>
@@ -2496,10 +2933,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>376</v>
       </c>
       <c r="B85">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C85">
         <v>100</v>
@@ -2510,10 +2947,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>377</v>
       </c>
       <c r="B86">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C86">
         <v>100</v>
@@ -2524,10 +2961,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>378</v>
       </c>
       <c r="B87">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C87">
         <v>100</v>
@@ -2538,10 +2975,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>379</v>
       </c>
       <c r="B88">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C88">
         <v>100</v>
@@ -2552,10 +2989,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="B89">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C89">
         <v>100</v>
@@ -2566,10 +3003,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>381</v>
       </c>
       <c r="B90">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C90">
         <v>100</v>
@@ -2580,10 +3017,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>382</v>
       </c>
       <c r="B91">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C91">
         <v>100</v>
@@ -2594,10 +3031,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>383</v>
       </c>
       <c r="B92">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C92">
         <v>100</v>
@@ -2608,10 +3045,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>384</v>
       </c>
       <c r="B93">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C93">
         <v>100</v>
@@ -2622,10 +3059,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B94">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C94">
         <v>100</v>
@@ -2636,10 +3073,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>386</v>
       </c>
       <c r="B95">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C95">
         <v>100</v>
@@ -2650,10 +3087,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>387</v>
       </c>
       <c r="B96">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C96">
         <v>100</v>
@@ -2664,10 +3101,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="B97">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C97">
         <v>100</v>
@@ -2678,10 +3115,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>389</v>
       </c>
       <c r="B98">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C98">
         <v>100</v>
@@ -2692,10 +3129,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>390</v>
       </c>
       <c r="B99">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C99">
         <v>100</v>
@@ -2706,10 +3143,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="B100">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C100">
         <v>100</v>
@@ -2720,10 +3157,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="B101">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C101">
         <v>100</v>
@@ -2734,10 +3171,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="B102">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C102">
         <v>100</v>
@@ -2748,10 +3185,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="B103">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C103">
         <v>100</v>
@@ -2762,10 +3199,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>395</v>
       </c>
       <c r="B104">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C104">
         <v>100</v>
@@ -2776,10 +3213,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="B105">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C105">
         <v>100</v>
@@ -2790,10 +3227,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>108</v>
+        <v>397</v>
       </c>
       <c r="B106">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C106">
         <v>100</v>
@@ -2804,10 +3241,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>398</v>
       </c>
       <c r="B107">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C107">
         <v>100</v>
@@ -2818,10 +3255,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>110</v>
+        <v>399</v>
       </c>
       <c r="B108">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C108">
         <v>100</v>
@@ -2832,10 +3269,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>400</v>
       </c>
       <c r="B109">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C109">
         <v>100</v>
@@ -2846,10 +3283,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>401</v>
       </c>
       <c r="B110">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C110">
         <v>100</v>
@@ -2860,10 +3297,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>113</v>
+        <v>402</v>
       </c>
       <c r="B111">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C111">
         <v>100</v>
@@ -2874,10 +3311,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>403</v>
       </c>
       <c r="B112">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C112">
         <v>100</v>
@@ -2888,10 +3325,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>404</v>
       </c>
       <c r="B113">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C113">
         <v>100</v>
@@ -2902,10 +3339,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>405</v>
       </c>
       <c r="B114">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C114">
         <v>100</v>
@@ -2916,10 +3353,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>406</v>
       </c>
       <c r="B115">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C115">
         <v>100</v>
@@ -2930,10 +3367,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>407</v>
       </c>
       <c r="B116">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -2944,10 +3381,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>408</v>
       </c>
       <c r="B117">
-        <v>100</v>
+        <v>376</v>
       </c>
       <c r="C117">
         <v>100</v>
@@ -2958,10 +3395,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>409</v>
       </c>
       <c r="B118">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C118">
         <v>100</v>
@@ -2972,10 +3409,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>410</v>
       </c>
       <c r="B119">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C119">
         <v>100</v>
@@ -2986,10 +3423,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="B120">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C120">
         <v>100</v>
@@ -3000,10 +3437,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>412</v>
       </c>
       <c r="B121">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C121">
         <v>100</v>
@@ -3014,10 +3451,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="B122">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C122">
         <v>100</v>
@@ -3028,10 +3465,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="B123">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C123">
         <v>100</v>
@@ -3042,10 +3479,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="B124">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C124">
         <v>100</v>
@@ -3056,10 +3493,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="B125">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C125">
         <v>100</v>
@@ -3070,10 +3507,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="B126">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C126">
         <v>100</v>
@@ -3084,10 +3521,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="B127">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C127">
         <v>100</v>
@@ -3098,10 +3535,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B128">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C128">
         <v>100</v>
@@ -3112,10 +3549,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B129">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C129">
         <v>100</v>
@@ -3126,10 +3563,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B130">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C130">
         <v>100</v>
@@ -3140,10 +3577,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B131">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C131">
         <v>100</v>
@@ -3154,10 +3591,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B132">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C132">
         <v>100</v>
@@ -3168,10 +3605,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B133">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C133">
         <v>100</v>
@@ -3182,10 +3619,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B134">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C134">
         <v>100</v>
@@ -3196,10 +3633,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B135">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C135">
         <v>100</v>
@@ -3210,10 +3647,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B136">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C136">
         <v>100</v>
@@ -3224,10 +3661,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B137">
-        <v>150</v>
+        <v>351</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -3238,10 +3675,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B138">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C138">
         <v>100</v>
@@ -3252,10 +3689,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B139">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C139">
         <v>100</v>
@@ -3266,10 +3703,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B140">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C140">
         <v>100</v>
@@ -3280,10 +3717,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="B141">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C141">
         <v>100</v>
@@ -3294,10 +3731,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B142">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C142">
         <v>100</v>
@@ -3308,10 +3745,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B143">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C143">
         <v>100</v>
@@ -3322,10 +3759,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B144">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C144">
         <v>100</v>
@@ -3336,10 +3773,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="B145">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C145">
         <v>100</v>
@@ -3350,10 +3787,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B146">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C146">
         <v>100</v>
@@ -3364,10 +3801,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B147">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C147">
         <v>100</v>
@@ -3378,10 +3815,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="B148">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C148">
         <v>100</v>
@@ -3392,10 +3829,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="B149">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C149">
         <v>100</v>
@@ -3406,10 +3843,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>152</v>
+        <v>311</v>
       </c>
       <c r="B150">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C150">
         <v>100</v>
@@ -3420,10 +3857,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>153</v>
+        <v>313</v>
       </c>
       <c r="B151">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C151">
         <v>100</v>
@@ -3434,10 +3871,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>154</v>
+        <v>312</v>
       </c>
       <c r="B152">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C152">
         <v>100</v>
@@ -3448,10 +3885,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="B153">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C153">
         <v>100</v>
@@ -3462,10 +3899,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="B154">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C154">
         <v>100</v>
@@ -3476,10 +3913,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="B155">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C155">
         <v>100</v>
@@ -3490,10 +3927,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="B156">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C156">
         <v>100</v>
@@ -3504,10 +3941,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="B157">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C157">
         <v>100</v>
@@ -3518,10 +3955,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="B158">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C158">
         <v>100</v>
@@ -3532,10 +3969,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>161</v>
+        <v>261</v>
       </c>
       <c r="B159">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C159">
         <v>100</v>
@@ -3546,10 +3983,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="B160">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C160">
         <v>100</v>
@@ -3560,10 +3997,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="B161">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C161">
         <v>100</v>
@@ -3574,10 +4011,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="B162">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C162">
         <v>100</v>
@@ -3588,10 +4025,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="B163">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C163">
         <v>100</v>
@@ -3602,10 +4039,10 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="B164">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C164">
         <v>100</v>
@@ -3616,10 +4053,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="B165">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C165">
         <v>100</v>
@@ -3630,10 +4067,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B166">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C166">
         <v>100</v>
@@ -3644,10 +4081,10 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="B167">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C167">
         <v>100</v>
@@ -3658,10 +4095,10 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="B168">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C168">
         <v>100</v>
@@ -3672,10 +4109,10 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="B169">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C169">
         <v>100</v>
@@ -3686,10 +4123,10 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="B170">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C170">
         <v>100</v>
@@ -3700,10 +4137,10 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="B171">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C171">
         <v>100</v>
@@ -3714,10 +4151,10 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="B172">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C172">
         <v>100</v>
@@ -3728,10 +4165,10 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="B173">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C173">
         <v>100</v>
@@ -3742,10 +4179,10 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="B174">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C174">
         <v>100</v>
@@ -3756,10 +4193,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="B175">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C175">
         <v>100</v>
@@ -3770,10 +4207,10 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="B176">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C176">
         <v>100</v>
@@ -3784,10 +4221,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="B177">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C177">
         <v>100</v>
@@ -3798,10 +4235,10 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="B178">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C178">
         <v>100</v>
@@ -3812,10 +4249,10 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="B179">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C179">
         <v>100</v>
@@ -3826,10 +4263,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="B180">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C180">
         <v>100</v>
@@ -3840,10 +4277,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="B181">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C181">
         <v>100</v>
@@ -3854,10 +4291,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="B182">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C182">
         <v>100</v>
@@ -3868,10 +4305,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="B183">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C183">
         <v>100</v>
@@ -3881,11 +4318,11 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184">
-        <v>1236</v>
+      <c r="A184" t="s">
+        <v>245</v>
       </c>
       <c r="B184">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C184">
         <v>100</v>
@@ -3895,11 +4332,11 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185">
-        <v>1237</v>
+      <c r="A185" t="s">
+        <v>247</v>
       </c>
       <c r="B185">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C185">
         <v>100</v>
@@ -3909,11 +4346,11 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <v>1238</v>
+      <c r="A186" t="s">
+        <v>246</v>
       </c>
       <c r="B186">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -3923,11 +4360,11 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <v>1239</v>
+      <c r="A187" t="s">
+        <v>244</v>
       </c>
       <c r="B187">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C187">
         <v>100</v>
@@ -3938,10 +4375,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>186</v>
+        <v>251</v>
       </c>
       <c r="B188">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C188">
         <v>100</v>
@@ -3951,11 +4388,11 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189">
-        <v>1231</v>
+      <c r="A189" t="s">
+        <v>248</v>
       </c>
       <c r="B189">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C189">
         <v>100</v>
@@ -3965,11 +4402,11 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190">
-        <v>1232</v>
+      <c r="A190" t="s">
+        <v>249</v>
       </c>
       <c r="B190">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C190">
         <v>100</v>
@@ -3979,11 +4416,11 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191">
-        <v>1233</v>
+      <c r="A191" t="s">
+        <v>250</v>
       </c>
       <c r="B191">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C191">
         <v>100</v>
@@ -3993,11 +4430,11 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192">
-        <v>1234</v>
+      <c r="A192" t="s">
+        <v>231</v>
       </c>
       <c r="B192">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C192">
         <v>100</v>
@@ -4007,11 +4444,11 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193">
-        <v>1235</v>
+      <c r="A193" t="s">
+        <v>228</v>
       </c>
       <c r="B193">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="C193">
         <v>100</v>
@@ -4022,10 +4459,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="B194">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C194">
         <v>100</v>
@@ -4035,11 +4472,11 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <v>1240</v>
+      <c r="A195" t="s">
+        <v>230</v>
       </c>
       <c r="B195">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C195">
         <v>100</v>
@@ -4049,11 +4486,11 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196">
-        <v>1241</v>
+      <c r="A196" t="s">
+        <v>314</v>
       </c>
       <c r="B196">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C196">
         <v>100</v>
@@ -4063,11 +4500,11 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197">
-        <v>1242</v>
+      <c r="A197" t="s">
+        <v>306</v>
       </c>
       <c r="B197">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C197">
         <v>100</v>
@@ -4077,11 +4514,11 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198">
-        <v>1243</v>
+      <c r="A198" t="s">
+        <v>308</v>
       </c>
       <c r="B198">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C198">
         <v>100</v>
@@ -4091,11 +4528,11 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199">
-        <v>1244</v>
+      <c r="A199" t="s">
+        <v>307</v>
       </c>
       <c r="B199">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C199">
         <v>100</v>
@@ -4106,10 +4543,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="B200">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C200">
         <v>100</v>
@@ -4120,10 +4557,10 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B201">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C201">
         <v>100</v>
@@ -4134,10 +4571,10 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B202">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C202">
         <v>100</v>
@@ -4148,10 +4585,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B203">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C203">
         <v>100</v>
@@ -4162,10 +4599,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B204">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C204">
         <v>100</v>
@@ -4176,10 +4613,10 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B205">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C205">
         <v>100</v>
@@ -4190,10 +4627,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B206">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C206">
         <v>100</v>
@@ -4204,10 +4641,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B207">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C207">
         <v>100</v>
@@ -4218,10 +4655,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B208">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C208">
         <v>100</v>
@@ -4232,10 +4669,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B209">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C209">
         <v>100</v>
@@ -4246,10 +4683,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B210">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C210">
         <v>100</v>
@@ -4260,10 +4697,10 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B211">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C211">
         <v>100</v>
@@ -4274,10 +4711,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B212">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C212">
         <v>100</v>
@@ -4288,10 +4725,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B213">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C213">
         <v>100</v>
@@ -4302,10 +4739,10 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B214">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C214">
         <v>100</v>
@@ -4316,10 +4753,10 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B215">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C215">
         <v>100</v>
@@ -4330,10 +4767,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B216">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C216">
         <v>100</v>
@@ -4344,10 +4781,10 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B217">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C217">
         <v>100</v>
@@ -4358,10 +4795,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B218">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C218">
         <v>100</v>
@@ -4372,10 +4809,10 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B219">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C219">
         <v>100</v>
@@ -4386,10 +4823,10 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B220">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C220">
         <v>100</v>
@@ -4400,10 +4837,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B221">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C221">
         <v>100</v>
@@ -4414,10 +4851,10 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B222">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C222">
         <v>100</v>
@@ -4428,10 +4865,10 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B223">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C223">
         <v>100</v>
@@ -4442,10 +4879,10 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B224">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C224">
         <v>100</v>
@@ -4456,10 +4893,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B225">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C225">
         <v>100</v>
@@ -4470,10 +4907,10 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B226">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C226">
         <v>100</v>
@@ -4484,10 +4921,10 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B227">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="C227">
         <v>100</v>
@@ -4498,10 +4935,10 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="B228">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C228">
         <v>100</v>
@@ -4512,10 +4949,10 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="B229">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C229">
         <v>100</v>
@@ -4526,10 +4963,10 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="B230">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C230">
         <v>100</v>
@@ -4540,10 +4977,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>219</v>
+        <v>299</v>
       </c>
       <c r="B231">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C231">
         <v>100</v>
@@ -4554,10 +4991,10 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="B232">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C232">
         <v>100</v>
@@ -4568,10 +5005,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="B233">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C233">
         <v>100</v>
@@ -4582,10 +5019,10 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>222</v>
+        <v>304</v>
       </c>
       <c r="B234">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C234">
         <v>100</v>
@@ -4596,10 +5033,10 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>223</v>
+        <v>303</v>
       </c>
       <c r="B235">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C235">
         <v>100</v>
@@ -4610,10 +5047,10 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="B236">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C236">
         <v>100</v>
@@ -4624,10 +5061,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="B237">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="C237">
         <v>100</v>
@@ -4638,10 +5075,10 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="B238">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C238">
         <v>100</v>
@@ -4652,10 +5089,10 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="B239">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C239">
         <v>100</v>
@@ -4666,10 +5103,10 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="B240">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C240">
         <v>100</v>
@@ -4680,10 +5117,10 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="B241">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C241">
         <v>100</v>
@@ -4694,10 +5131,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="B242">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C242">
         <v>100</v>
@@ -4708,10 +5145,10 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="B243">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C243">
         <v>100</v>
@@ -4722,10 +5159,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="B244">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -4736,10 +5173,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="B245">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C245">
         <v>100</v>
@@ -4750,10 +5187,10 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="B246">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C246">
         <v>100</v>
@@ -4764,10 +5201,10 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="B247">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C247">
         <v>100</v>
@@ -4778,10 +5215,10 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="B248">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C248">
         <v>100</v>
@@ -4792,10 +5229,10 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B249">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C249">
         <v>100</v>
@@ -4806,10 +5243,10 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="B250">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C250">
         <v>100</v>
@@ -4820,10 +5257,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B251">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C251">
         <v>100</v>
@@ -4834,10 +5271,10 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="B252">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C252">
         <v>100</v>
@@ -4848,10 +5285,10 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="B253">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C253">
         <v>100</v>
@@ -4862,10 +5299,10 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="B254">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C254">
         <v>100</v>
@@ -4876,10 +5313,10 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B255">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C255">
         <v>100</v>
@@ -4890,10 +5327,10 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="B256">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C256">
         <v>100</v>
@@ -4904,10 +5341,10 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B257">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C257">
         <v>100</v>
@@ -4918,10 +5355,10 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B258">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C258">
         <v>100</v>
@@ -4932,10 +5369,10 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B259">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C259">
         <v>100</v>
@@ -4946,10 +5383,10 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B260">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C260">
         <v>100</v>
@@ -4960,10 +5397,10 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B261">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C261">
         <v>100</v>
@@ -4974,10 +5411,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B262">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C262">
         <v>100</v>
@@ -4988,10 +5425,10 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B263">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C263">
         <v>100</v>
@@ -5002,10 +5439,10 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B264">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C264">
         <v>100</v>
@@ -5016,10 +5453,10 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="B265">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C265">
         <v>100</v>
@@ -5030,10 +5467,10 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="B266">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C266">
         <v>100</v>
@@ -5044,10 +5481,10 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="B267">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C267">
         <v>100</v>
@@ -5058,10 +5495,10 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="B268">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C268">
         <v>100</v>
@@ -5072,10 +5509,10 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="B269">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C269">
         <v>100</v>
@@ -5086,10 +5523,10 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="B270">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C270">
         <v>100</v>
@@ -5100,10 +5537,10 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="B271">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C271">
         <v>100</v>
@@ -5114,10 +5551,10 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B272">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C272">
         <v>100</v>
@@ -5128,10 +5565,10 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B273">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C273">
         <v>100</v>
@@ -5142,10 +5579,10 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B274">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -5156,10 +5593,10 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B275">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -5170,10 +5607,10 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="B276">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C276">
         <v>100</v>
@@ -5184,10 +5621,10 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B277">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C277">
         <v>100</v>
@@ -5198,10 +5635,10 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="B278">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C278">
         <v>100</v>
@@ -5212,10 +5649,10 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="B279">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C279">
         <v>100</v>
@@ -5226,10 +5663,10 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>269</v>
+        <v>180</v>
       </c>
       <c r="B280">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C280">
         <v>100</v>
@@ -5240,10 +5677,10 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>270</v>
+        <v>181</v>
       </c>
       <c r="B281">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C281">
         <v>100</v>
@@ -5254,10 +5691,10 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="B282">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C282">
         <v>100</v>
@@ -5268,10 +5705,10 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>272</v>
+        <v>184</v>
       </c>
       <c r="B283">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C283">
         <v>100</v>
@@ -5282,10 +5719,10 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>273</v>
+        <v>413</v>
       </c>
       <c r="B284">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C284">
         <v>100</v>
@@ -5296,10 +5733,10 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="B285">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C285">
         <v>100</v>
@@ -5310,10 +5747,10 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>275</v>
+        <v>162</v>
       </c>
       <c r="B286">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C286">
         <v>100</v>
@@ -5324,10 +5761,10 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="B287">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C287">
         <v>100</v>
@@ -5338,10 +5775,10 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="B288">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C288">
         <v>100</v>
@@ -5352,10 +5789,10 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="B289">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C289">
         <v>100</v>
@@ -5366,10 +5803,10 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="B290">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C290">
         <v>100</v>
@@ -5380,10 +5817,10 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>280</v>
+        <v>165</v>
       </c>
       <c r="B291">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C291">
         <v>100</v>
@@ -5394,10 +5831,10 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="B292">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C292">
         <v>100</v>
@@ -5408,10 +5845,10 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>282</v>
+        <v>166</v>
       </c>
       <c r="B293">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C293">
         <v>100</v>
@@ -5422,10 +5859,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="B294">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C294">
         <v>100</v>
@@ -5436,10 +5873,10 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="B295">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="C295">
         <v>100</v>
@@ -5450,10 +5887,10 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>285</v>
+        <v>415</v>
       </c>
       <c r="B296">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="C296">
         <v>100</v>
@@ -5464,10 +5901,10 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>286</v>
+        <v>416</v>
       </c>
       <c r="B297">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="C297">
         <v>100</v>
@@ -5478,10 +5915,10 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>287</v>
+        <v>417</v>
       </c>
       <c r="B298">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C298">
         <v>100</v>
@@ -5492,10 +5929,10 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>288</v>
+        <v>418</v>
       </c>
       <c r="B299">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C299">
         <v>100</v>
@@ -5506,10 +5943,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>289</v>
+        <v>419</v>
       </c>
       <c r="B300">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C300">
         <v>100</v>
@@ -5520,10 +5957,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>290</v>
+        <v>420</v>
       </c>
       <c r="B301">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C301">
         <v>100</v>
@@ -5534,10 +5971,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>291</v>
+        <v>421</v>
       </c>
       <c r="B302">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C302">
         <v>100</v>
@@ -5548,10 +5985,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>292</v>
+        <v>422</v>
       </c>
       <c r="B303">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C303">
         <v>100</v>
@@ -5562,10 +5999,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>293</v>
+        <v>423</v>
       </c>
       <c r="B304">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C304">
         <v>100</v>
@@ -5576,10 +6013,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>294</v>
+        <v>424</v>
       </c>
       <c r="B305">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C305">
         <v>100</v>
@@ -5590,10 +6027,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="B306">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="C306">
         <v>100</v>
@@ -5604,10 +6041,10 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>296</v>
+        <v>148</v>
       </c>
       <c r="B307">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C307">
         <v>100</v>
@@ -5618,10 +6055,10 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>297</v>
+        <v>145</v>
       </c>
       <c r="B308">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C308">
         <v>100</v>
@@ -5632,10 +6069,10 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>298</v>
+        <v>146</v>
       </c>
       <c r="B309">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C309">
         <v>100</v>
@@ -5646,10 +6083,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>299</v>
+        <v>147</v>
       </c>
       <c r="B310">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C310">
         <v>100</v>
@@ -5660,10 +6097,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="B311">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C311">
         <v>100</v>
@@ -5674,10 +6111,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>301</v>
+        <v>141</v>
       </c>
       <c r="B312">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C312">
         <v>100</v>
@@ -5688,10 +6125,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>302</v>
+        <v>142</v>
       </c>
       <c r="B313">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C313">
         <v>100</v>
@@ -5702,10 +6139,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>303</v>
+        <v>143</v>
       </c>
       <c r="B314">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C314">
         <v>100</v>
@@ -5716,10 +6153,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>304</v>
+        <v>140</v>
       </c>
       <c r="B315">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="C315">
         <v>100</v>
@@ -5730,10 +6167,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>305</v>
+        <v>132</v>
       </c>
       <c r="B316">
-        <v>150</v>
+        <v>311</v>
       </c>
       <c r="C316">
         <v>100</v>
@@ -5744,10 +6181,10 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>306</v>
+        <v>134</v>
       </c>
       <c r="B317">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C317">
         <v>100</v>
@@ -5758,10 +6195,10 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>307</v>
+        <v>130</v>
       </c>
       <c r="B318">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C318">
         <v>100</v>
@@ -5772,10 +6209,10 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>308</v>
+        <v>133</v>
       </c>
       <c r="B319">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C319">
         <v>100</v>
@@ -5786,10 +6223,10 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="B320">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C320">
         <v>100</v>
@@ -5800,10 +6237,10 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>310</v>
+        <v>136</v>
       </c>
       <c r="B321">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C321">
         <v>100</v>
@@ -5814,10 +6251,10 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
+        <v>139</v>
+      </c>
+      <c r="B322">
         <v>311</v>
-      </c>
-      <c r="B322">
-        <v>225</v>
       </c>
       <c r="C322">
         <v>100</v>
@@ -5828,10 +6265,10 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>312</v>
+        <v>138</v>
       </c>
       <c r="B323">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C323">
         <v>100</v>
@@ -5842,10 +6279,10 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>313</v>
+        <v>135</v>
       </c>
       <c r="B324">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C324">
         <v>100</v>
@@ -5856,15 +6293,1863 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>314</v>
+        <v>137</v>
       </c>
       <c r="B325">
-        <v>225</v>
+        <v>311</v>
       </c>
       <c r="C325">
         <v>100</v>
       </c>
       <c r="D325" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>128</v>
+      </c>
+      <c r="B326">
+        <v>206</v>
+      </c>
+      <c r="C326">
+        <v>100</v>
+      </c>
+      <c r="D326" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>126</v>
+      </c>
+      <c r="B327">
+        <v>206</v>
+      </c>
+      <c r="C327">
+        <v>100</v>
+      </c>
+      <c r="D327" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>129</v>
+      </c>
+      <c r="B328">
+        <v>206</v>
+      </c>
+      <c r="C328">
+        <v>100</v>
+      </c>
+      <c r="D328" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>124</v>
+      </c>
+      <c r="B329">
+        <v>206</v>
+      </c>
+      <c r="C329">
+        <v>100</v>
+      </c>
+      <c r="D329" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>125</v>
+      </c>
+      <c r="B330">
+        <v>206</v>
+      </c>
+      <c r="C330">
+        <v>100</v>
+      </c>
+      <c r="D330" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>127</v>
+      </c>
+      <c r="B331">
+        <v>206</v>
+      </c>
+      <c r="C331">
+        <v>100</v>
+      </c>
+      <c r="D331" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>118</v>
+      </c>
+      <c r="B332">
+        <v>206</v>
+      </c>
+      <c r="C332">
+        <v>100</v>
+      </c>
+      <c r="D332" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>119</v>
+      </c>
+      <c r="B333">
+        <v>206</v>
+      </c>
+      <c r="C333">
+        <v>100</v>
+      </c>
+      <c r="D333" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>121</v>
+      </c>
+      <c r="B334">
+        <v>206</v>
+      </c>
+      <c r="C334">
+        <v>100</v>
+      </c>
+      <c r="D334" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>122</v>
+      </c>
+      <c r="B335">
+        <v>206</v>
+      </c>
+      <c r="C335">
+        <v>100</v>
+      </c>
+      <c r="D335" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>123</v>
+      </c>
+      <c r="B336">
+        <v>206</v>
+      </c>
+      <c r="C336">
+        <v>100</v>
+      </c>
+      <c r="D336" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>120</v>
+      </c>
+      <c r="B337">
+        <v>206</v>
+      </c>
+      <c r="C337">
+        <v>100</v>
+      </c>
+      <c r="D337" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>64</v>
+      </c>
+      <c r="B338">
+        <v>206</v>
+      </c>
+      <c r="C338">
+        <v>100</v>
+      </c>
+      <c r="D338" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>67</v>
+      </c>
+      <c r="B339">
+        <v>206</v>
+      </c>
+      <c r="C339">
+        <v>100</v>
+      </c>
+      <c r="D339" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>68</v>
+      </c>
+      <c r="B340">
+        <v>206</v>
+      </c>
+      <c r="C340">
+        <v>100</v>
+      </c>
+      <c r="D340" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>65</v>
+      </c>
+      <c r="B341">
+        <v>206</v>
+      </c>
+      <c r="C341">
+        <v>100</v>
+      </c>
+      <c r="D341" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>69</v>
+      </c>
+      <c r="B342">
+        <v>206</v>
+      </c>
+      <c r="C342">
+        <v>100</v>
+      </c>
+      <c r="D342" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>66</v>
+      </c>
+      <c r="B343">
+        <v>206</v>
+      </c>
+      <c r="C343">
+        <v>100</v>
+      </c>
+      <c r="D343" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>75</v>
+      </c>
+      <c r="B344">
+        <v>206</v>
+      </c>
+      <c r="C344">
+        <v>100</v>
+      </c>
+      <c r="D344" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>72</v>
+      </c>
+      <c r="B345">
+        <v>206</v>
+      </c>
+      <c r="C345">
+        <v>100</v>
+      </c>
+      <c r="D345" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>71</v>
+      </c>
+      <c r="B346">
+        <v>206</v>
+      </c>
+      <c r="C346">
+        <v>100</v>
+      </c>
+      <c r="D346" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>70</v>
+      </c>
+      <c r="B347">
+        <v>206</v>
+      </c>
+      <c r="C347">
+        <v>100</v>
+      </c>
+      <c r="D347" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>73</v>
+      </c>
+      <c r="B348">
+        <v>206</v>
+      </c>
+      <c r="C348">
+        <v>100</v>
+      </c>
+      <c r="D348" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>74</v>
+      </c>
+      <c r="B349">
+        <v>206</v>
+      </c>
+      <c r="C349">
+        <v>100</v>
+      </c>
+      <c r="D349" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>97</v>
+      </c>
+      <c r="B350">
+        <v>311</v>
+      </c>
+      <c r="C350">
+        <v>100</v>
+      </c>
+      <c r="D350" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>95</v>
+      </c>
+      <c r="B351">
+        <v>311</v>
+      </c>
+      <c r="C351">
+        <v>100</v>
+      </c>
+      <c r="D351" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>94</v>
+      </c>
+      <c r="B352">
+        <v>311</v>
+      </c>
+      <c r="C352">
+        <v>100</v>
+      </c>
+      <c r="D352" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>96</v>
+      </c>
+      <c r="B353">
+        <v>311</v>
+      </c>
+      <c r="C353">
+        <v>100</v>
+      </c>
+      <c r="D353" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>93</v>
+      </c>
+      <c r="B354">
+        <v>311</v>
+      </c>
+      <c r="C354">
+        <v>100</v>
+      </c>
+      <c r="D354" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>116</v>
+      </c>
+      <c r="B355">
+        <v>311</v>
+      </c>
+      <c r="C355">
+        <v>100</v>
+      </c>
+      <c r="D355" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>114</v>
+      </c>
+      <c r="B356">
+        <v>311</v>
+      </c>
+      <c r="C356">
+        <v>100</v>
+      </c>
+      <c r="D356" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>115</v>
+      </c>
+      <c r="B357">
+        <v>311</v>
+      </c>
+      <c r="C357">
+        <v>100</v>
+      </c>
+      <c r="D357" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>113</v>
+      </c>
+      <c r="B358">
+        <v>311</v>
+      </c>
+      <c r="C358">
+        <v>100</v>
+      </c>
+      <c r="D358" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>117</v>
+      </c>
+      <c r="B359">
+        <v>311</v>
+      </c>
+      <c r="C359">
+        <v>100</v>
+      </c>
+      <c r="D359" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>102</v>
+      </c>
+      <c r="B360">
+        <v>311</v>
+      </c>
+      <c r="C360">
+        <v>100</v>
+      </c>
+      <c r="D360" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>99</v>
+      </c>
+      <c r="B361">
+        <v>311</v>
+      </c>
+      <c r="C361">
+        <v>100</v>
+      </c>
+      <c r="D361" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>101</v>
+      </c>
+      <c r="B362">
+        <v>311</v>
+      </c>
+      <c r="C362">
+        <v>100</v>
+      </c>
+      <c r="D362" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>100</v>
+      </c>
+      <c r="B363">
+        <v>311</v>
+      </c>
+      <c r="C363">
+        <v>100</v>
+      </c>
+      <c r="D363" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>98</v>
+      </c>
+      <c r="B364">
+        <v>311</v>
+      </c>
+      <c r="C364">
+        <v>100</v>
+      </c>
+      <c r="D364" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>89</v>
+      </c>
+      <c r="B365">
+        <v>311</v>
+      </c>
+      <c r="C365">
+        <v>100</v>
+      </c>
+      <c r="D365" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>90</v>
+      </c>
+      <c r="B366">
+        <v>311</v>
+      </c>
+      <c r="C366">
+        <v>100</v>
+      </c>
+      <c r="D366" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>92</v>
+      </c>
+      <c r="B367">
+        <v>311</v>
+      </c>
+      <c r="C367">
+        <v>100</v>
+      </c>
+      <c r="D367" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>91</v>
+      </c>
+      <c r="B368">
+        <v>311</v>
+      </c>
+      <c r="C368">
+        <v>100</v>
+      </c>
+      <c r="D368" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>88</v>
+      </c>
+      <c r="B369">
+        <v>311</v>
+      </c>
+      <c r="C369">
+        <v>100</v>
+      </c>
+      <c r="D369" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>109</v>
+      </c>
+      <c r="B370">
+        <v>311</v>
+      </c>
+      <c r="C370">
+        <v>100</v>
+      </c>
+      <c r="D370" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>110</v>
+      </c>
+      <c r="B371">
+        <v>311</v>
+      </c>
+      <c r="C371">
+        <v>100</v>
+      </c>
+      <c r="D371" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>111</v>
+      </c>
+      <c r="B372">
+        <v>311</v>
+      </c>
+      <c r="C372">
+        <v>100</v>
+      </c>
+      <c r="D372" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>112</v>
+      </c>
+      <c r="B373">
+        <v>311</v>
+      </c>
+      <c r="C373">
+        <v>100</v>
+      </c>
+      <c r="D373" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>108</v>
+      </c>
+      <c r="B374">
+        <v>311</v>
+      </c>
+      <c r="C374">
+        <v>100</v>
+      </c>
+      <c r="D374" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>106</v>
+      </c>
+      <c r="B375">
+        <v>311</v>
+      </c>
+      <c r="C375">
+        <v>100</v>
+      </c>
+      <c r="D375" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>103</v>
+      </c>
+      <c r="B376">
+        <v>311</v>
+      </c>
+      <c r="C376">
+        <v>100</v>
+      </c>
+      <c r="D376" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>107</v>
+      </c>
+      <c r="B377">
+        <v>311</v>
+      </c>
+      <c r="C377">
+        <v>100</v>
+      </c>
+      <c r="D377" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>105</v>
+      </c>
+      <c r="B378">
+        <v>311</v>
+      </c>
+      <c r="C378">
+        <v>100</v>
+      </c>
+      <c r="D378" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>104</v>
+      </c>
+      <c r="B379">
+        <v>311</v>
+      </c>
+      <c r="C379">
+        <v>100</v>
+      </c>
+      <c r="D379" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>80</v>
+      </c>
+      <c r="B380">
+        <v>206</v>
+      </c>
+      <c r="C380">
+        <v>100</v>
+      </c>
+      <c r="D380" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>78</v>
+      </c>
+      <c r="B381">
+        <v>206</v>
+      </c>
+      <c r="C381">
+        <v>100</v>
+      </c>
+      <c r="D381" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>79</v>
+      </c>
+      <c r="B382">
+        <v>206</v>
+      </c>
+      <c r="C382">
+        <v>100</v>
+      </c>
+      <c r="D382" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>77</v>
+      </c>
+      <c r="B383">
+        <v>206</v>
+      </c>
+      <c r="C383">
+        <v>100</v>
+      </c>
+      <c r="D383" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>76</v>
+      </c>
+      <c r="B384">
+        <v>206</v>
+      </c>
+      <c r="C384">
+        <v>100</v>
+      </c>
+      <c r="D384" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>81</v>
+      </c>
+      <c r="B385">
+        <v>206</v>
+      </c>
+      <c r="C385">
+        <v>100</v>
+      </c>
+      <c r="D385" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>83</v>
+      </c>
+      <c r="B386">
+        <v>206</v>
+      </c>
+      <c r="C386">
+        <v>100</v>
+      </c>
+      <c r="D386" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>82</v>
+      </c>
+      <c r="B387">
+        <v>206</v>
+      </c>
+      <c r="C387">
+        <v>100</v>
+      </c>
+      <c r="D387" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>87</v>
+      </c>
+      <c r="B388">
+        <v>206</v>
+      </c>
+      <c r="C388">
+        <v>100</v>
+      </c>
+      <c r="D388" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>85</v>
+      </c>
+      <c r="B389">
+        <v>206</v>
+      </c>
+      <c r="C389">
+        <v>100</v>
+      </c>
+      <c r="D389" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>84</v>
+      </c>
+      <c r="B390">
+        <v>206</v>
+      </c>
+      <c r="C390">
+        <v>100</v>
+      </c>
+      <c r="D390" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>86</v>
+      </c>
+      <c r="B391">
+        <v>206</v>
+      </c>
+      <c r="C391">
+        <v>100</v>
+      </c>
+      <c r="D391" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>60</v>
+      </c>
+      <c r="B392">
+        <v>301</v>
+      </c>
+      <c r="C392">
+        <v>100</v>
+      </c>
+      <c r="D392" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>62</v>
+      </c>
+      <c r="B393">
+        <v>301</v>
+      </c>
+      <c r="C393">
+        <v>100</v>
+      </c>
+      <c r="D393" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>61</v>
+      </c>
+      <c r="B394">
+        <v>301</v>
+      </c>
+      <c r="C394">
+        <v>100</v>
+      </c>
+      <c r="D394" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>63</v>
+      </c>
+      <c r="B395">
+        <v>301</v>
+      </c>
+      <c r="C395">
+        <v>100</v>
+      </c>
+      <c r="D395" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>59</v>
+      </c>
+      <c r="B396">
+        <v>301</v>
+      </c>
+      <c r="C396">
+        <v>100</v>
+      </c>
+      <c r="D396" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>40</v>
+      </c>
+      <c r="B397">
+        <v>301</v>
+      </c>
+      <c r="C397">
+        <v>100</v>
+      </c>
+      <c r="D397" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>39</v>
+      </c>
+      <c r="B398">
+        <v>301</v>
+      </c>
+      <c r="C398">
+        <v>100</v>
+      </c>
+      <c r="D398" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>42</v>
+      </c>
+      <c r="B399">
+        <v>301</v>
+      </c>
+      <c r="C399">
+        <v>100</v>
+      </c>
+      <c r="D399" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>43</v>
+      </c>
+      <c r="B400">
+        <v>301</v>
+      </c>
+      <c r="C400">
+        <v>100</v>
+      </c>
+      <c r="D400" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>41</v>
+      </c>
+      <c r="B401">
+        <v>301</v>
+      </c>
+      <c r="C401">
+        <v>100</v>
+      </c>
+      <c r="D401" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>45</v>
+      </c>
+      <c r="B402">
+        <v>301</v>
+      </c>
+      <c r="C402">
+        <v>100</v>
+      </c>
+      <c r="D402" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>47</v>
+      </c>
+      <c r="B403">
+        <v>301</v>
+      </c>
+      <c r="C403">
+        <v>100</v>
+      </c>
+      <c r="D403" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>48</v>
+      </c>
+      <c r="B404">
+        <v>301</v>
+      </c>
+      <c r="C404">
+        <v>100</v>
+      </c>
+      <c r="D404" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>44</v>
+      </c>
+      <c r="B405">
+        <v>301</v>
+      </c>
+      <c r="C405">
+        <v>100</v>
+      </c>
+      <c r="D405" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>46</v>
+      </c>
+      <c r="B406">
+        <v>301</v>
+      </c>
+      <c r="C406">
+        <v>100</v>
+      </c>
+      <c r="D406" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>58</v>
+      </c>
+      <c r="B407">
+        <v>301</v>
+      </c>
+      <c r="C407">
+        <v>100</v>
+      </c>
+      <c r="D407" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>54</v>
+      </c>
+      <c r="B408">
+        <v>301</v>
+      </c>
+      <c r="C408">
+        <v>100</v>
+      </c>
+      <c r="D408" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>56</v>
+      </c>
+      <c r="B409">
+        <v>301</v>
+      </c>
+      <c r="C409">
+        <v>100</v>
+      </c>
+      <c r="D409" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>57</v>
+      </c>
+      <c r="B410">
+        <v>301</v>
+      </c>
+      <c r="C410">
+        <v>100</v>
+      </c>
+      <c r="D410" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>55</v>
+      </c>
+      <c r="B411">
+        <v>301</v>
+      </c>
+      <c r="C411">
+        <v>100</v>
+      </c>
+      <c r="D411" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>49</v>
+      </c>
+      <c r="B412">
+        <v>301</v>
+      </c>
+      <c r="C412">
+        <v>100</v>
+      </c>
+      <c r="D412" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>53</v>
+      </c>
+      <c r="B413">
+        <v>301</v>
+      </c>
+      <c r="C413">
+        <v>100</v>
+      </c>
+      <c r="D413" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>50</v>
+      </c>
+      <c r="B414">
+        <v>301</v>
+      </c>
+      <c r="C414">
+        <v>100</v>
+      </c>
+      <c r="D414" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415">
+        <v>301</v>
+      </c>
+      <c r="C415">
+        <v>100</v>
+      </c>
+      <c r="D415" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>51</v>
+      </c>
+      <c r="B416">
+        <v>301</v>
+      </c>
+      <c r="C416">
+        <v>100</v>
+      </c>
+      <c r="D416" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>34</v>
+      </c>
+      <c r="B417">
+        <v>301</v>
+      </c>
+      <c r="C417">
+        <v>100</v>
+      </c>
+      <c r="D417" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>35</v>
+      </c>
+      <c r="B418">
+        <v>301</v>
+      </c>
+      <c r="C418">
+        <v>100</v>
+      </c>
+      <c r="D418" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>37</v>
+      </c>
+      <c r="B419">
+        <v>301</v>
+      </c>
+      <c r="C419">
+        <v>100</v>
+      </c>
+      <c r="D419" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>36</v>
+      </c>
+      <c r="B420">
+        <v>301</v>
+      </c>
+      <c r="C420">
+        <v>100</v>
+      </c>
+      <c r="D420" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>38</v>
+      </c>
+      <c r="B421">
+        <v>301</v>
+      </c>
+      <c r="C421">
+        <v>100</v>
+      </c>
+      <c r="D421" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>425</v>
+      </c>
+      <c r="B422">
+        <v>426</v>
+      </c>
+      <c r="C422">
+        <v>100</v>
+      </c>
+      <c r="D422" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>426</v>
+      </c>
+      <c r="B423">
+        <v>426</v>
+      </c>
+      <c r="C423">
+        <v>100</v>
+      </c>
+      <c r="D423" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>427</v>
+      </c>
+      <c r="B424">
+        <v>426</v>
+      </c>
+      <c r="C424">
+        <v>100</v>
+      </c>
+      <c r="D424" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>428</v>
+      </c>
+      <c r="B425">
+        <v>426</v>
+      </c>
+      <c r="C425">
+        <v>100</v>
+      </c>
+      <c r="D425" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>429</v>
+      </c>
+      <c r="B426">
+        <v>426</v>
+      </c>
+      <c r="C426">
+        <v>100</v>
+      </c>
+      <c r="D426" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>430</v>
+      </c>
+      <c r="B427">
+        <v>426</v>
+      </c>
+      <c r="C427">
+        <v>100</v>
+      </c>
+      <c r="D427" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>431</v>
+      </c>
+      <c r="B428">
+        <v>426</v>
+      </c>
+      <c r="C428">
+        <v>100</v>
+      </c>
+      <c r="D428" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>432</v>
+      </c>
+      <c r="B429">
+        <v>426</v>
+      </c>
+      <c r="C429">
+        <v>100</v>
+      </c>
+      <c r="D429" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>433</v>
+      </c>
+      <c r="B430">
+        <v>351</v>
+      </c>
+      <c r="C430">
+        <v>100</v>
+      </c>
+      <c r="D430" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>434</v>
+      </c>
+      <c r="B431">
+        <v>351</v>
+      </c>
+      <c r="C431">
+        <v>100</v>
+      </c>
+      <c r="D431" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>435</v>
+      </c>
+      <c r="B432">
+        <v>351</v>
+      </c>
+      <c r="C432">
+        <v>100</v>
+      </c>
+      <c r="D432" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>436</v>
+      </c>
+      <c r="B433">
+        <v>351</v>
+      </c>
+      <c r="C433">
+        <v>100</v>
+      </c>
+      <c r="D433" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>437</v>
+      </c>
+      <c r="B434">
+        <v>426</v>
+      </c>
+      <c r="C434">
+        <v>100</v>
+      </c>
+      <c r="D434" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>438</v>
+      </c>
+      <c r="B435">
+        <v>426</v>
+      </c>
+      <c r="C435">
+        <v>100</v>
+      </c>
+      <c r="D435" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>439</v>
+      </c>
+      <c r="B436">
+        <v>426</v>
+      </c>
+      <c r="C436">
+        <v>100</v>
+      </c>
+      <c r="D436" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>440</v>
+      </c>
+      <c r="B437">
+        <v>426</v>
+      </c>
+      <c r="C437">
+        <v>100</v>
+      </c>
+      <c r="D437" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>441</v>
+      </c>
+      <c r="B438">
+        <v>426</v>
+      </c>
+      <c r="C438">
+        <v>100</v>
+      </c>
+      <c r="D438" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>442</v>
+      </c>
+      <c r="B439">
+        <v>426</v>
+      </c>
+      <c r="C439">
+        <v>100</v>
+      </c>
+      <c r="D439" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>443</v>
+      </c>
+      <c r="B440">
+        <v>426</v>
+      </c>
+      <c r="C440">
+        <v>100</v>
+      </c>
+      <c r="D440" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>444</v>
+      </c>
+      <c r="B441">
+        <v>426</v>
+      </c>
+      <c r="C441">
+        <v>100</v>
+      </c>
+      <c r="D441" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>445</v>
+      </c>
+      <c r="B442">
+        <v>351</v>
+      </c>
+      <c r="C442">
+        <v>100</v>
+      </c>
+      <c r="D442" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>446</v>
+      </c>
+      <c r="B443">
+        <v>351</v>
+      </c>
+      <c r="C443">
+        <v>100</v>
+      </c>
+      <c r="D443" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>447</v>
+      </c>
+      <c r="B444">
+        <v>351</v>
+      </c>
+      <c r="C444">
+        <v>100</v>
+      </c>
+      <c r="D444" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>448</v>
+      </c>
+      <c r="B445">
+        <v>351</v>
+      </c>
+      <c r="C445">
+        <v>100</v>
+      </c>
+      <c r="D445" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>449</v>
+      </c>
+      <c r="B446">
+        <v>351</v>
+      </c>
+      <c r="C446">
+        <v>100</v>
+      </c>
+      <c r="D446" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>450</v>
+      </c>
+      <c r="B447">
+        <v>351</v>
+      </c>
+      <c r="C447">
+        <v>100</v>
+      </c>
+      <c r="D447" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>451</v>
+      </c>
+      <c r="B448">
+        <v>351</v>
+      </c>
+      <c r="C448">
+        <v>100</v>
+      </c>
+      <c r="D448" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>452</v>
+      </c>
+      <c r="B449">
+        <v>351</v>
+      </c>
+      <c r="C449">
+        <v>100</v>
+      </c>
+      <c r="D449" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>453</v>
+      </c>
+      <c r="B450">
+        <v>351</v>
+      </c>
+      <c r="C450">
+        <v>100</v>
+      </c>
+      <c r="D450" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>454</v>
+      </c>
+      <c r="B451">
+        <v>351</v>
+      </c>
+      <c r="C451">
+        <v>100</v>
+      </c>
+      <c r="D451" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>455</v>
+      </c>
+      <c r="B452">
+        <v>351</v>
+      </c>
+      <c r="C452">
+        <v>100</v>
+      </c>
+      <c r="D452" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>456</v>
+      </c>
+      <c r="B453">
+        <v>351</v>
+      </c>
+      <c r="C453">
+        <v>100</v>
+      </c>
+      <c r="D453" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>457</v>
+      </c>
+      <c r="B454">
+        <v>351</v>
+      </c>
+      <c r="C454">
+        <v>100</v>
+      </c>
+      <c r="D454" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>458</v>
+      </c>
+      <c r="B455">
+        <v>351</v>
+      </c>
+      <c r="C455">
+        <v>100</v>
+      </c>
+      <c r="D455" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>459</v>
+      </c>
+      <c r="B456">
+        <v>351</v>
+      </c>
+      <c r="C456">
+        <v>100</v>
+      </c>
+      <c r="D456" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>460</v>
+      </c>
+      <c r="B457">
+        <v>351</v>
+      </c>
+      <c r="C457">
+        <v>100</v>
+      </c>
+      <c r="D457" t="s">
         <v>252</v>
       </c>
     </row>

--- a/maliyetler.xlsx
+++ b/maliyetler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FA63D2-74F4-4168-9B4B-9CDC8E5BA35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4110D8F-37E8-4FB1-BAFB-499C22A8583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$D$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$D$457</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4938,7 +4938,7 @@
         <v>300</v>
       </c>
       <c r="B228">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C228">
         <v>100</v>
@@ -4952,7 +4952,7 @@
         <v>296</v>
       </c>
       <c r="B229">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C229">
         <v>100</v>
@@ -4966,7 +4966,7 @@
         <v>297</v>
       </c>
       <c r="B230">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C230">
         <v>100</v>
@@ -4980,7 +4980,7 @@
         <v>299</v>
       </c>
       <c r="B231">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C231">
         <v>100</v>
@@ -4994,7 +4994,7 @@
         <v>298</v>
       </c>
       <c r="B232">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C232">
         <v>100</v>
@@ -5008,7 +5008,7 @@
         <v>301</v>
       </c>
       <c r="B233">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C233">
         <v>100</v>
@@ -5022,7 +5022,7 @@
         <v>304</v>
       </c>
       <c r="B234">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C234">
         <v>100</v>
@@ -5036,7 +5036,7 @@
         <v>303</v>
       </c>
       <c r="B235">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C235">
         <v>100</v>
@@ -5050,7 +5050,7 @@
         <v>302</v>
       </c>
       <c r="B236">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C236">
         <v>100</v>
@@ -5064,7 +5064,7 @@
         <v>305</v>
       </c>
       <c r="B237">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C237">
         <v>100</v>
@@ -6170,7 +6170,7 @@
         <v>132</v>
       </c>
       <c r="B316">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C316">
         <v>100</v>
@@ -6184,7 +6184,7 @@
         <v>134</v>
       </c>
       <c r="B317">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C317">
         <v>100</v>
@@ -6198,7 +6198,7 @@
         <v>130</v>
       </c>
       <c r="B318">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C318">
         <v>100</v>
@@ -6212,7 +6212,7 @@
         <v>133</v>
       </c>
       <c r="B319">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C319">
         <v>100</v>
@@ -6226,7 +6226,7 @@
         <v>131</v>
       </c>
       <c r="B320">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C320">
         <v>100</v>
@@ -6240,7 +6240,7 @@
         <v>136</v>
       </c>
       <c r="B321">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C321">
         <v>100</v>
@@ -6254,7 +6254,7 @@
         <v>139</v>
       </c>
       <c r="B322">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C322">
         <v>100</v>
@@ -6268,7 +6268,7 @@
         <v>138</v>
       </c>
       <c r="B323">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C323">
         <v>100</v>
@@ -6282,7 +6282,7 @@
         <v>135</v>
       </c>
       <c r="B324">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C324">
         <v>100</v>
@@ -6296,7 +6296,7 @@
         <v>137</v>
       </c>
       <c r="B325">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C325">
         <v>100</v>
@@ -6646,7 +6646,7 @@
         <v>97</v>
       </c>
       <c r="B350">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C350">
         <v>100</v>
@@ -6660,7 +6660,7 @@
         <v>95</v>
       </c>
       <c r="B351">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C351">
         <v>100</v>
@@ -6674,7 +6674,7 @@
         <v>94</v>
       </c>
       <c r="B352">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C352">
         <v>100</v>
@@ -6688,7 +6688,7 @@
         <v>96</v>
       </c>
       <c r="B353">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C353">
         <v>100</v>
@@ -6702,7 +6702,7 @@
         <v>93</v>
       </c>
       <c r="B354">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C354">
         <v>100</v>
@@ -6716,7 +6716,7 @@
         <v>116</v>
       </c>
       <c r="B355">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C355">
         <v>100</v>
@@ -6730,7 +6730,7 @@
         <v>114</v>
       </c>
       <c r="B356">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C356">
         <v>100</v>
@@ -6744,7 +6744,7 @@
         <v>115</v>
       </c>
       <c r="B357">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C357">
         <v>100</v>
@@ -6758,7 +6758,7 @@
         <v>113</v>
       </c>
       <c r="B358">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C358">
         <v>100</v>
@@ -6772,7 +6772,7 @@
         <v>117</v>
       </c>
       <c r="B359">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C359">
         <v>100</v>
@@ -6786,7 +6786,7 @@
         <v>102</v>
       </c>
       <c r="B360">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C360">
         <v>100</v>
@@ -6800,7 +6800,7 @@
         <v>99</v>
       </c>
       <c r="B361">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C361">
         <v>100</v>
@@ -6814,7 +6814,7 @@
         <v>101</v>
       </c>
       <c r="B362">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C362">
         <v>100</v>
@@ -6828,7 +6828,7 @@
         <v>100</v>
       </c>
       <c r="B363">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C363">
         <v>100</v>
@@ -6842,7 +6842,7 @@
         <v>98</v>
       </c>
       <c r="B364">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C364">
         <v>100</v>
@@ -6856,7 +6856,7 @@
         <v>89</v>
       </c>
       <c r="B365">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C365">
         <v>100</v>
@@ -6870,7 +6870,7 @@
         <v>90</v>
       </c>
       <c r="B366">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C366">
         <v>100</v>
@@ -6884,7 +6884,7 @@
         <v>92</v>
       </c>
       <c r="B367">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C367">
         <v>100</v>
@@ -6898,7 +6898,7 @@
         <v>91</v>
       </c>
       <c r="B368">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C368">
         <v>100</v>
@@ -6912,7 +6912,7 @@
         <v>88</v>
       </c>
       <c r="B369">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C369">
         <v>100</v>
@@ -6926,7 +6926,7 @@
         <v>109</v>
       </c>
       <c r="B370">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C370">
         <v>100</v>
@@ -6940,7 +6940,7 @@
         <v>110</v>
       </c>
       <c r="B371">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C371">
         <v>100</v>
@@ -6954,7 +6954,7 @@
         <v>111</v>
       </c>
       <c r="B372">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C372">
         <v>100</v>
@@ -6968,7 +6968,7 @@
         <v>112</v>
       </c>
       <c r="B373">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C373">
         <v>100</v>
@@ -6982,7 +6982,7 @@
         <v>108</v>
       </c>
       <c r="B374">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C374">
         <v>100</v>
@@ -6996,7 +6996,7 @@
         <v>106</v>
       </c>
       <c r="B375">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C375">
         <v>100</v>
@@ -7010,7 +7010,7 @@
         <v>103</v>
       </c>
       <c r="B376">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C376">
         <v>100</v>
@@ -7024,7 +7024,7 @@
         <v>107</v>
       </c>
       <c r="B377">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C377">
         <v>100</v>
@@ -7038,7 +7038,7 @@
         <v>105</v>
       </c>
       <c r="B378">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C378">
         <v>100</v>
@@ -7052,7 +7052,7 @@
         <v>104</v>
       </c>
       <c r="B379">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="C379">
         <v>100</v>
@@ -8154,6 +8154,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D457" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/maliyetler.xlsx
+++ b/maliyetler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soner\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4110D8F-37E8-4FB1-BAFB-499C22A8583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D13BD-FA0F-45F7-9DA6-BBEE9588E28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1752,7 +1752,7 @@
     <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1774,7 +1774,7 @@
         <v>315</v>
       </c>
       <c r="B2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1788,7 +1788,7 @@
         <v>316</v>
       </c>
       <c r="B3">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1802,7 +1802,7 @@
         <v>317</v>
       </c>
       <c r="B4">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1816,7 +1816,7 @@
         <v>318</v>
       </c>
       <c r="B5">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1830,7 +1830,7 @@
         <v>319</v>
       </c>
       <c r="B6">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1844,7 +1844,7 @@
         <v>320</v>
       </c>
       <c r="B7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1858,7 +1858,7 @@
         <v>321</v>
       </c>
       <c r="B8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1872,7 +1872,7 @@
         <v>322</v>
       </c>
       <c r="B9">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1886,7 +1886,7 @@
         <v>323</v>
       </c>
       <c r="B10">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1900,7 +1900,7 @@
         <v>324</v>
       </c>
       <c r="B11">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1914,7 +1914,7 @@
         <v>4</v>
       </c>
       <c r="B12">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1956,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1970,7 +1970,7 @@
         <v>8</v>
       </c>
       <c r="B16">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1984,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="B17">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1998,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="B18">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -2012,7 +2012,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -2026,7 +2026,7 @@
         <v>12</v>
       </c>
       <c r="B20">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -2040,7 +2040,7 @@
         <v>13</v>
       </c>
       <c r="B21">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -2054,7 +2054,7 @@
         <v>14</v>
       </c>
       <c r="B22">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -2068,7 +2068,7 @@
         <v>15</v>
       </c>
       <c r="B23">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -2082,7 +2082,7 @@
         <v>16</v>
       </c>
       <c r="B24">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -2096,7 +2096,7 @@
         <v>17</v>
       </c>
       <c r="B25">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -2110,7 +2110,7 @@
         <v>18</v>
       </c>
       <c r="B26">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -2124,7 +2124,7 @@
         <v>19</v>
       </c>
       <c r="B27">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -2138,7 +2138,7 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -2152,7 +2152,7 @@
         <v>21</v>
       </c>
       <c r="B29">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -2166,7 +2166,7 @@
         <v>22</v>
       </c>
       <c r="B30">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -2180,7 +2180,7 @@
         <v>23</v>
       </c>
       <c r="B31">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2194,7 +2194,7 @@
         <v>24</v>
       </c>
       <c r="B32">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -2208,7 +2208,7 @@
         <v>25</v>
       </c>
       <c r="B33">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2222,7 +2222,7 @@
         <v>325</v>
       </c>
       <c r="B34">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -2236,7 +2236,7 @@
         <v>326</v>
       </c>
       <c r="B35">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2250,7 +2250,7 @@
         <v>327</v>
       </c>
       <c r="B36">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -2264,7 +2264,7 @@
         <v>328</v>
       </c>
       <c r="B37">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2278,7 +2278,7 @@
         <v>329</v>
       </c>
       <c r="B38">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -2292,7 +2292,7 @@
         <v>330</v>
       </c>
       <c r="B39">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2306,7 +2306,7 @@
         <v>331</v>
       </c>
       <c r="B40">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -2320,7 +2320,7 @@
         <v>332</v>
       </c>
       <c r="B41">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -2334,7 +2334,7 @@
         <v>333</v>
       </c>
       <c r="B42">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -2348,7 +2348,7 @@
         <v>334</v>
       </c>
       <c r="B43">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -2362,7 +2362,7 @@
         <v>335</v>
       </c>
       <c r="B44">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -2376,7 +2376,7 @@
         <v>336</v>
       </c>
       <c r="B45">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -2390,7 +2390,7 @@
         <v>337</v>
       </c>
       <c r="B46">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2404,7 +2404,7 @@
         <v>338</v>
       </c>
       <c r="B47">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -2418,7 +2418,7 @@
         <v>339</v>
       </c>
       <c r="B48">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -2432,7 +2432,7 @@
         <v>340</v>
       </c>
       <c r="B49">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C49">
         <v>100</v>
@@ -2446,7 +2446,7 @@
         <v>341</v>
       </c>
       <c r="B50">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2460,7 +2460,7 @@
         <v>342</v>
       </c>
       <c r="B51">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C51">
         <v>100</v>
@@ -2474,7 +2474,7 @@
         <v>343</v>
       </c>
       <c r="B52">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C52">
         <v>100</v>
@@ -2488,7 +2488,7 @@
         <v>344</v>
       </c>
       <c r="B53">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C53">
         <v>100</v>
@@ -2502,7 +2502,7 @@
         <v>345</v>
       </c>
       <c r="B54">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C54">
         <v>100</v>
@@ -2516,7 +2516,7 @@
         <v>346</v>
       </c>
       <c r="B55">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C55">
         <v>100</v>
@@ -2530,7 +2530,7 @@
         <v>347</v>
       </c>
       <c r="B56">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C56">
         <v>100</v>
@@ -2544,7 +2544,7 @@
         <v>348</v>
       </c>
       <c r="B57">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C57">
         <v>100</v>
@@ -2558,7 +2558,7 @@
         <v>349</v>
       </c>
       <c r="B58">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C58">
         <v>100</v>
@@ -2572,7 +2572,7 @@
         <v>350</v>
       </c>
       <c r="B59">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C59">
         <v>100</v>
@@ -2586,7 +2586,7 @@
         <v>351</v>
       </c>
       <c r="B60">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C60">
         <v>100</v>
@@ -2600,7 +2600,7 @@
         <v>352</v>
       </c>
       <c r="B61">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C61">
         <v>100</v>
@@ -2614,7 +2614,7 @@
         <v>353</v>
       </c>
       <c r="B62">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C62">
         <v>100</v>
@@ -2628,7 +2628,7 @@
         <v>354</v>
       </c>
       <c r="B63">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C63">
         <v>100</v>
@@ -2642,7 +2642,7 @@
         <v>355</v>
       </c>
       <c r="B64">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C64">
         <v>100</v>
@@ -2656,7 +2656,7 @@
         <v>356</v>
       </c>
       <c r="B65">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C65">
         <v>100</v>
@@ -2670,7 +2670,7 @@
         <v>357</v>
       </c>
       <c r="B66">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C66">
         <v>100</v>
@@ -2684,7 +2684,7 @@
         <v>358</v>
       </c>
       <c r="B67">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C67">
         <v>100</v>
@@ -2698,7 +2698,7 @@
         <v>359</v>
       </c>
       <c r="B68">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C68">
         <v>100</v>
@@ -2712,7 +2712,7 @@
         <v>360</v>
       </c>
       <c r="B69">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C69">
         <v>100</v>
@@ -2726,7 +2726,7 @@
         <v>361</v>
       </c>
       <c r="B70">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -2740,7 +2740,7 @@
         <v>362</v>
       </c>
       <c r="B71">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C71">
         <v>100</v>
@@ -2754,7 +2754,7 @@
         <v>363</v>
       </c>
       <c r="B72">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C72">
         <v>100</v>
@@ -2768,7 +2768,7 @@
         <v>364</v>
       </c>
       <c r="B73">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C73">
         <v>100</v>
@@ -2782,7 +2782,7 @@
         <v>365</v>
       </c>
       <c r="B74">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C74">
         <v>100</v>
@@ -2796,7 +2796,7 @@
         <v>366</v>
       </c>
       <c r="B75">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C75">
         <v>100</v>
@@ -2810,7 +2810,7 @@
         <v>367</v>
       </c>
       <c r="B76">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C76">
         <v>100</v>
@@ -2824,7 +2824,7 @@
         <v>368</v>
       </c>
       <c r="B77">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C77">
         <v>100</v>
@@ -2838,7 +2838,7 @@
         <v>369</v>
       </c>
       <c r="B78">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C78">
         <v>100</v>
@@ -2852,7 +2852,7 @@
         <v>370</v>
       </c>
       <c r="B79">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C79">
         <v>100</v>
@@ -2866,7 +2866,7 @@
         <v>371</v>
       </c>
       <c r="B80">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C80">
         <v>100</v>
@@ -2880,7 +2880,7 @@
         <v>372</v>
       </c>
       <c r="B81">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C81">
         <v>100</v>
@@ -2894,7 +2894,7 @@
         <v>373</v>
       </c>
       <c r="B82">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C82">
         <v>100</v>
@@ -2908,7 +2908,7 @@
         <v>374</v>
       </c>
       <c r="B83">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C83">
         <v>100</v>
@@ -2922,7 +2922,7 @@
         <v>375</v>
       </c>
       <c r="B84">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C84">
         <v>100</v>
@@ -2936,7 +2936,7 @@
         <v>376</v>
       </c>
       <c r="B85">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C85">
         <v>100</v>
@@ -2950,7 +2950,7 @@
         <v>377</v>
       </c>
       <c r="B86">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C86">
         <v>100</v>
@@ -2964,7 +2964,7 @@
         <v>378</v>
       </c>
       <c r="B87">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C87">
         <v>100</v>
@@ -2978,7 +2978,7 @@
         <v>379</v>
       </c>
       <c r="B88">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C88">
         <v>100</v>
@@ -2992,7 +2992,7 @@
         <v>380</v>
       </c>
       <c r="B89">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C89">
         <v>100</v>
@@ -3006,7 +3006,7 @@
         <v>381</v>
       </c>
       <c r="B90">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C90">
         <v>100</v>
@@ -3020,7 +3020,7 @@
         <v>382</v>
       </c>
       <c r="B91">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C91">
         <v>100</v>
@@ -3034,7 +3034,7 @@
         <v>383</v>
       </c>
       <c r="B92">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C92">
         <v>100</v>
@@ -3048,7 +3048,7 @@
         <v>384</v>
       </c>
       <c r="B93">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C93">
         <v>100</v>
@@ -3062,7 +3062,7 @@
         <v>385</v>
       </c>
       <c r="B94">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C94">
         <v>100</v>
@@ -3076,7 +3076,7 @@
         <v>386</v>
       </c>
       <c r="B95">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C95">
         <v>100</v>
@@ -3090,7 +3090,7 @@
         <v>387</v>
       </c>
       <c r="B96">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C96">
         <v>100</v>
@@ -3104,7 +3104,7 @@
         <v>388</v>
       </c>
       <c r="B97">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C97">
         <v>100</v>
@@ -3118,7 +3118,7 @@
         <v>389</v>
       </c>
       <c r="B98">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C98">
         <v>100</v>
@@ -3132,7 +3132,7 @@
         <v>390</v>
       </c>
       <c r="B99">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C99">
         <v>100</v>
@@ -3146,7 +3146,7 @@
         <v>391</v>
       </c>
       <c r="B100">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C100">
         <v>100</v>
@@ -3160,7 +3160,7 @@
         <v>392</v>
       </c>
       <c r="B101">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C101">
         <v>100</v>
@@ -3174,7 +3174,7 @@
         <v>393</v>
       </c>
       <c r="B102">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C102">
         <v>100</v>
@@ -3188,7 +3188,7 @@
         <v>394</v>
       </c>
       <c r="B103">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C103">
         <v>100</v>
@@ -3202,7 +3202,7 @@
         <v>395</v>
       </c>
       <c r="B104">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C104">
         <v>100</v>
@@ -3216,7 +3216,7 @@
         <v>396</v>
       </c>
       <c r="B105">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C105">
         <v>100</v>
@@ -3230,7 +3230,7 @@
         <v>397</v>
       </c>
       <c r="B106">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C106">
         <v>100</v>
@@ -3244,7 +3244,7 @@
         <v>398</v>
       </c>
       <c r="B107">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C107">
         <v>100</v>
@@ -3258,7 +3258,7 @@
         <v>399</v>
       </c>
       <c r="B108">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C108">
         <v>100</v>
@@ -3272,7 +3272,7 @@
         <v>400</v>
       </c>
       <c r="B109">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C109">
         <v>100</v>
@@ -3286,7 +3286,7 @@
         <v>401</v>
       </c>
       <c r="B110">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C110">
         <v>100</v>
@@ -3300,7 +3300,7 @@
         <v>402</v>
       </c>
       <c r="B111">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C111">
         <v>100</v>
@@ -3314,7 +3314,7 @@
         <v>403</v>
       </c>
       <c r="B112">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C112">
         <v>100</v>
@@ -3328,7 +3328,7 @@
         <v>404</v>
       </c>
       <c r="B113">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C113">
         <v>100</v>
@@ -3342,7 +3342,7 @@
         <v>405</v>
       </c>
       <c r="B114">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C114">
         <v>100</v>
@@ -3356,7 +3356,7 @@
         <v>406</v>
       </c>
       <c r="B115">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C115">
         <v>100</v>
@@ -3370,7 +3370,7 @@
         <v>407</v>
       </c>
       <c r="B116">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C116">
         <v>100</v>
@@ -3384,7 +3384,7 @@
         <v>408</v>
       </c>
       <c r="B117">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C117">
         <v>100</v>
@@ -3398,7 +3398,7 @@
         <v>409</v>
       </c>
       <c r="B118">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C118">
         <v>100</v>
@@ -3412,7 +3412,7 @@
         <v>410</v>
       </c>
       <c r="B119">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C119">
         <v>100</v>
@@ -3426,7 +3426,7 @@
         <v>411</v>
       </c>
       <c r="B120">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C120">
         <v>100</v>
@@ -3440,7 +3440,7 @@
         <v>412</v>
       </c>
       <c r="B121">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C121">
         <v>100</v>
@@ -3454,7 +3454,7 @@
         <v>26</v>
       </c>
       <c r="B122">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C122">
         <v>100</v>
@@ -3468,7 +3468,7 @@
         <v>27</v>
       </c>
       <c r="B123">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C123">
         <v>100</v>
@@ -3482,7 +3482,7 @@
         <v>28</v>
       </c>
       <c r="B124">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C124">
         <v>100</v>
@@ -3496,7 +3496,7 @@
         <v>29</v>
       </c>
       <c r="B125">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C125">
         <v>100</v>
@@ -3510,7 +3510,7 @@
         <v>30</v>
       </c>
       <c r="B126">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C126">
         <v>100</v>
@@ -3524,7 +3524,7 @@
         <v>31</v>
       </c>
       <c r="B127">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C127">
         <v>100</v>
@@ -3538,7 +3538,7 @@
         <v>32</v>
       </c>
       <c r="B128">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C128">
         <v>100</v>
@@ -3552,7 +3552,7 @@
         <v>33</v>
       </c>
       <c r="B129">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C129">
         <v>100</v>
@@ -3566,7 +3566,7 @@
         <v>150</v>
       </c>
       <c r="B130">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C130">
         <v>100</v>
@@ -3580,7 +3580,7 @@
         <v>151</v>
       </c>
       <c r="B131">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C131">
         <v>100</v>
@@ -3594,7 +3594,7 @@
         <v>152</v>
       </c>
       <c r="B132">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C132">
         <v>100</v>
@@ -3608,7 +3608,7 @@
         <v>153</v>
       </c>
       <c r="B133">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C133">
         <v>100</v>
@@ -3622,7 +3622,7 @@
         <v>154</v>
       </c>
       <c r="B134">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C134">
         <v>100</v>
@@ -3636,7 +3636,7 @@
         <v>155</v>
       </c>
       <c r="B135">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C135">
         <v>100</v>
@@ -3650,7 +3650,7 @@
         <v>156</v>
       </c>
       <c r="B136">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C136">
         <v>100</v>
@@ -3664,7 +3664,7 @@
         <v>157</v>
       </c>
       <c r="B137">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C137">
         <v>100</v>
@@ -3678,7 +3678,7 @@
         <v>158</v>
       </c>
       <c r="B138">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C138">
         <v>100</v>
@@ -3692,7 +3692,7 @@
         <v>159</v>
       </c>
       <c r="B139">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C139">
         <v>100</v>
@@ -3706,7 +3706,7 @@
         <v>170</v>
       </c>
       <c r="B140">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C140">
         <v>100</v>
@@ -3720,7 +3720,7 @@
         <v>171</v>
       </c>
       <c r="B141">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C141">
         <v>100</v>
@@ -3734,7 +3734,7 @@
         <v>172</v>
       </c>
       <c r="B142">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C142">
         <v>100</v>
@@ -3748,7 +3748,7 @@
         <v>173</v>
       </c>
       <c r="B143">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C143">
         <v>100</v>
@@ -3762,7 +3762,7 @@
         <v>174</v>
       </c>
       <c r="B144">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C144">
         <v>100</v>
@@ -3776,7 +3776,7 @@
         <v>175</v>
       </c>
       <c r="B145">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C145">
         <v>100</v>
@@ -3790,7 +3790,7 @@
         <v>176</v>
       </c>
       <c r="B146">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C146">
         <v>100</v>
@@ -3804,7 +3804,7 @@
         <v>177</v>
       </c>
       <c r="B147">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C147">
         <v>100</v>
@@ -3818,7 +3818,7 @@
         <v>178</v>
       </c>
       <c r="B148">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C148">
         <v>100</v>
@@ -3832,7 +3832,7 @@
         <v>179</v>
       </c>
       <c r="B149">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C149">
         <v>100</v>
@@ -3846,7 +3846,7 @@
         <v>311</v>
       </c>
       <c r="B150">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C150">
         <v>100</v>
@@ -3860,7 +3860,7 @@
         <v>313</v>
       </c>
       <c r="B151">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C151">
         <v>100</v>
@@ -3874,7 +3874,7 @@
         <v>312</v>
       </c>
       <c r="B152">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C152">
         <v>100</v>
@@ -3888,7 +3888,7 @@
         <v>310</v>
       </c>
       <c r="B153">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C153">
         <v>100</v>
@@ -3902,7 +3902,7 @@
         <v>253</v>
       </c>
       <c r="B154">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C154">
         <v>100</v>
@@ -3916,7 +3916,7 @@
         <v>256</v>
       </c>
       <c r="B155">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C155">
         <v>100</v>
@@ -3930,7 +3930,7 @@
         <v>254</v>
       </c>
       <c r="B156">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C156">
         <v>100</v>
@@ -3944,7 +3944,7 @@
         <v>255</v>
       </c>
       <c r="B157">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C157">
         <v>100</v>
@@ -3958,7 +3958,7 @@
         <v>257</v>
       </c>
       <c r="B158">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C158">
         <v>100</v>
@@ -3972,7 +3972,7 @@
         <v>261</v>
       </c>
       <c r="B159">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C159">
         <v>100</v>
@@ -3986,7 +3986,7 @@
         <v>260</v>
       </c>
       <c r="B160">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C160">
         <v>100</v>
@@ -4000,7 +4000,7 @@
         <v>258</v>
       </c>
       <c r="B161">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C161">
         <v>100</v>
@@ -4014,7 +4014,7 @@
         <v>262</v>
       </c>
       <c r="B162">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C162">
         <v>100</v>
@@ -4028,7 +4028,7 @@
         <v>259</v>
       </c>
       <c r="B163">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C163">
         <v>100</v>
@@ -4042,7 +4042,7 @@
         <v>239</v>
       </c>
       <c r="B164">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C164">
         <v>100</v>
@@ -4056,7 +4056,7 @@
         <v>238</v>
       </c>
       <c r="B165">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C165">
         <v>100</v>
@@ -4070,7 +4070,7 @@
         <v>237</v>
       </c>
       <c r="B166">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C166">
         <v>100</v>
@@ -4084,7 +4084,7 @@
         <v>236</v>
       </c>
       <c r="B167">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C167">
         <v>100</v>
@@ -4098,7 +4098,7 @@
         <v>234</v>
       </c>
       <c r="B168">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C168">
         <v>100</v>
@@ -4112,7 +4112,7 @@
         <v>233</v>
       </c>
       <c r="B169">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C169">
         <v>100</v>
@@ -4126,7 +4126,7 @@
         <v>232</v>
       </c>
       <c r="B170">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C170">
         <v>100</v>
@@ -4140,7 +4140,7 @@
         <v>235</v>
       </c>
       <c r="B171">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C171">
         <v>100</v>
@@ -4154,7 +4154,7 @@
         <v>223</v>
       </c>
       <c r="B172">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C172">
         <v>100</v>
@@ -4168,7 +4168,7 @@
         <v>220</v>
       </c>
       <c r="B173">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C173">
         <v>100</v>
@@ -4182,7 +4182,7 @@
         <v>222</v>
       </c>
       <c r="B174">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C174">
         <v>100</v>
@@ -4196,7 +4196,7 @@
         <v>221</v>
       </c>
       <c r="B175">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C175">
         <v>100</v>
@@ -4210,7 +4210,7 @@
         <v>227</v>
       </c>
       <c r="B176">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C176">
         <v>100</v>
@@ -4224,7 +4224,7 @@
         <v>225</v>
       </c>
       <c r="B177">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C177">
         <v>100</v>
@@ -4238,7 +4238,7 @@
         <v>226</v>
       </c>
       <c r="B178">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C178">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>224</v>
       </c>
       <c r="B179">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C179">
         <v>100</v>
@@ -4266,7 +4266,7 @@
         <v>242</v>
       </c>
       <c r="B180">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C180">
         <v>100</v>
@@ -4280,7 +4280,7 @@
         <v>240</v>
       </c>
       <c r="B181">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C181">
         <v>100</v>
@@ -4294,7 +4294,7 @@
         <v>241</v>
       </c>
       <c r="B182">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C182">
         <v>100</v>
@@ -4308,7 +4308,7 @@
         <v>243</v>
       </c>
       <c r="B183">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C183">
         <v>100</v>
@@ -4322,7 +4322,7 @@
         <v>245</v>
       </c>
       <c r="B184">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C184">
         <v>100</v>
@@ -4336,7 +4336,7 @@
         <v>247</v>
       </c>
       <c r="B185">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C185">
         <v>100</v>
@@ -4350,7 +4350,7 @@
         <v>246</v>
       </c>
       <c r="B186">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C186">
         <v>100</v>
@@ -4364,7 +4364,7 @@
         <v>244</v>
       </c>
       <c r="B187">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C187">
         <v>100</v>
@@ -4378,7 +4378,7 @@
         <v>251</v>
       </c>
       <c r="B188">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C188">
         <v>100</v>
@@ -4392,7 +4392,7 @@
         <v>248</v>
       </c>
       <c r="B189">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C189">
         <v>100</v>
@@ -4406,7 +4406,7 @@
         <v>249</v>
       </c>
       <c r="B190">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C190">
         <v>100</v>
@@ -4420,7 +4420,7 @@
         <v>250</v>
       </c>
       <c r="B191">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C191">
         <v>100</v>
@@ -4434,7 +4434,7 @@
         <v>231</v>
       </c>
       <c r="B192">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C192">
         <v>100</v>
@@ -4448,7 +4448,7 @@
         <v>228</v>
       </c>
       <c r="B193">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C193">
         <v>100</v>
@@ -4462,7 +4462,7 @@
         <v>229</v>
       </c>
       <c r="B194">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C194">
         <v>100</v>
@@ -4476,7 +4476,7 @@
         <v>230</v>
       </c>
       <c r="B195">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C195">
         <v>100</v>
@@ -4490,7 +4490,7 @@
         <v>314</v>
       </c>
       <c r="B196">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C196">
         <v>100</v>
@@ -4504,7 +4504,7 @@
         <v>306</v>
       </c>
       <c r="B197">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C197">
         <v>100</v>
@@ -4518,7 +4518,7 @@
         <v>308</v>
       </c>
       <c r="B198">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C198">
         <v>100</v>
@@ -4532,7 +4532,7 @@
         <v>307</v>
       </c>
       <c r="B199">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C199">
         <v>100</v>
@@ -4546,7 +4546,7 @@
         <v>309</v>
       </c>
       <c r="B200">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C200">
         <v>100</v>
@@ -4560,7 +4560,7 @@
         <v>186</v>
       </c>
       <c r="B201">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C201">
         <v>100</v>
@@ -4574,7 +4574,7 @@
         <v>188</v>
       </c>
       <c r="B202">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C202">
         <v>100</v>
@@ -4588,7 +4588,7 @@
         <v>189</v>
       </c>
       <c r="B203">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C203">
         <v>100</v>
@@ -4602,7 +4602,7 @@
         <v>190</v>
       </c>
       <c r="B204">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C204">
         <v>100</v>
@@ -4616,7 +4616,7 @@
         <v>191</v>
       </c>
       <c r="B205">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C205">
         <v>100</v>
@@ -4630,7 +4630,7 @@
         <v>192</v>
       </c>
       <c r="B206">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C206">
         <v>100</v>
@@ -4644,7 +4644,7 @@
         <v>193</v>
       </c>
       <c r="B207">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C207">
         <v>100</v>
@@ -4658,7 +4658,7 @@
         <v>194</v>
       </c>
       <c r="B208">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C208">
         <v>100</v>
@@ -4672,7 +4672,7 @@
         <v>195</v>
       </c>
       <c r="B209">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C209">
         <v>100</v>
@@ -4686,7 +4686,7 @@
         <v>196</v>
       </c>
       <c r="B210">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C210">
         <v>100</v>
@@ -4700,7 +4700,7 @@
         <v>197</v>
       </c>
       <c r="B211">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C211">
         <v>100</v>
@@ -4714,7 +4714,7 @@
         <v>198</v>
       </c>
       <c r="B212">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C212">
         <v>100</v>
@@ -4728,7 +4728,7 @@
         <v>199</v>
       </c>
       <c r="B213">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C213">
         <v>100</v>
@@ -4742,7 +4742,7 @@
         <v>200</v>
       </c>
       <c r="B214">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C214">
         <v>100</v>
@@ -4756,7 +4756,7 @@
         <v>201</v>
       </c>
       <c r="B215">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C215">
         <v>100</v>
@@ -4770,7 +4770,7 @@
         <v>202</v>
       </c>
       <c r="B216">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C216">
         <v>100</v>
@@ -4784,7 +4784,7 @@
         <v>203</v>
       </c>
       <c r="B217">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C217">
         <v>100</v>
@@ -4798,7 +4798,7 @@
         <v>204</v>
       </c>
       <c r="B218">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C218">
         <v>100</v>
@@ -4812,7 +4812,7 @@
         <v>205</v>
       </c>
       <c r="B219">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C219">
         <v>100</v>
@@ -4826,7 +4826,7 @@
         <v>206</v>
       </c>
       <c r="B220">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C220">
         <v>100</v>
@@ -4840,7 +4840,7 @@
         <v>207</v>
       </c>
       <c r="B221">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C221">
         <v>100</v>
@@ -4854,7 +4854,7 @@
         <v>208</v>
       </c>
       <c r="B222">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C222">
         <v>100</v>
@@ -4868,7 +4868,7 @@
         <v>209</v>
       </c>
       <c r="B223">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C223">
         <v>100</v>
@@ -4882,7 +4882,7 @@
         <v>210</v>
       </c>
       <c r="B224">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C224">
         <v>100</v>
@@ -4896,7 +4896,7 @@
         <v>211</v>
       </c>
       <c r="B225">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C225">
         <v>100</v>
@@ -4910,7 +4910,7 @@
         <v>212</v>
       </c>
       <c r="B226">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C226">
         <v>100</v>
@@ -4924,7 +4924,7 @@
         <v>213</v>
       </c>
       <c r="B227">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C227">
         <v>100</v>
@@ -4938,7 +4938,7 @@
         <v>300</v>
       </c>
       <c r="B228">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C228">
         <v>100</v>
@@ -4952,7 +4952,7 @@
         <v>296</v>
       </c>
       <c r="B229">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C229">
         <v>100</v>
@@ -4966,7 +4966,7 @@
         <v>297</v>
       </c>
       <c r="B230">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C230">
         <v>100</v>
@@ -4980,7 +4980,7 @@
         <v>299</v>
       </c>
       <c r="B231">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C231">
         <v>100</v>
@@ -4994,7 +4994,7 @@
         <v>298</v>
       </c>
       <c r="B232">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C232">
         <v>100</v>
@@ -5008,7 +5008,7 @@
         <v>301</v>
       </c>
       <c r="B233">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C233">
         <v>100</v>
@@ -5022,7 +5022,7 @@
         <v>304</v>
       </c>
       <c r="B234">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C234">
         <v>100</v>
@@ -5036,7 +5036,7 @@
         <v>303</v>
       </c>
       <c r="B235">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C235">
         <v>100</v>
@@ -5050,7 +5050,7 @@
         <v>302</v>
       </c>
       <c r="B236">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C236">
         <v>100</v>
@@ -5064,7 +5064,7 @@
         <v>305</v>
       </c>
       <c r="B237">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C237">
         <v>100</v>
@@ -5078,7 +5078,7 @@
         <v>287</v>
       </c>
       <c r="B238">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C238">
         <v>100</v>
@@ -5092,7 +5092,7 @@
         <v>286</v>
       </c>
       <c r="B239">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C239">
         <v>100</v>
@@ -5106,7 +5106,7 @@
         <v>288</v>
       </c>
       <c r="B240">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C240">
         <v>100</v>
@@ -5120,7 +5120,7 @@
         <v>289</v>
       </c>
       <c r="B241">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C241">
         <v>100</v>
@@ -5134,7 +5134,7 @@
         <v>290</v>
       </c>
       <c r="B242">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C242">
         <v>100</v>
@@ -5148,7 +5148,7 @@
         <v>291</v>
       </c>
       <c r="B243">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C243">
         <v>100</v>
@@ -5162,7 +5162,7 @@
         <v>293</v>
       </c>
       <c r="B244">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C244">
         <v>100</v>
@@ -5176,7 +5176,7 @@
         <v>294</v>
       </c>
       <c r="B245">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C245">
         <v>100</v>
@@ -5190,7 +5190,7 @@
         <v>292</v>
       </c>
       <c r="B246">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C246">
         <v>100</v>
@@ -5204,7 +5204,7 @@
         <v>295</v>
       </c>
       <c r="B247">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C247">
         <v>100</v>
@@ -5218,7 +5218,7 @@
         <v>214</v>
       </c>
       <c r="B248">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C248">
         <v>100</v>
@@ -5232,7 +5232,7 @@
         <v>215</v>
       </c>
       <c r="B249">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C249">
         <v>100</v>
@@ -5246,7 +5246,7 @@
         <v>216</v>
       </c>
       <c r="B250">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C250">
         <v>100</v>
@@ -5260,7 +5260,7 @@
         <v>217</v>
       </c>
       <c r="B251">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C251">
         <v>100</v>
@@ -5274,7 +5274,7 @@
         <v>218</v>
       </c>
       <c r="B252">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C252">
         <v>100</v>
@@ -5288,7 +5288,7 @@
         <v>219</v>
       </c>
       <c r="B253">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C253">
         <v>100</v>
@@ -5302,7 +5302,7 @@
         <v>187</v>
       </c>
       <c r="B254">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C254">
         <v>100</v>
@@ -5316,7 +5316,7 @@
         <v>263</v>
       </c>
       <c r="B255">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C255">
         <v>100</v>
@@ -5330,7 +5330,7 @@
         <v>264</v>
       </c>
       <c r="B256">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C256">
         <v>100</v>
@@ -5344,7 +5344,7 @@
         <v>265</v>
       </c>
       <c r="B257">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C257">
         <v>100</v>
@@ -5358,7 +5358,7 @@
         <v>266</v>
       </c>
       <c r="B258">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C258">
         <v>100</v>
@@ -5372,7 +5372,7 @@
         <v>267</v>
       </c>
       <c r="B259">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C259">
         <v>100</v>
@@ -5386,7 +5386,7 @@
         <v>268</v>
       </c>
       <c r="B260">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C260">
         <v>100</v>
@@ -5400,7 +5400,7 @@
         <v>269</v>
       </c>
       <c r="B261">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C261">
         <v>100</v>
@@ -5414,7 +5414,7 @@
         <v>270</v>
       </c>
       <c r="B262">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C262">
         <v>100</v>
@@ -5428,7 +5428,7 @@
         <v>271</v>
       </c>
       <c r="B263">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C263">
         <v>100</v>
@@ -5442,7 +5442,7 @@
         <v>272</v>
       </c>
       <c r="B264">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C264">
         <v>100</v>
@@ -5456,7 +5456,7 @@
         <v>273</v>
       </c>
       <c r="B265">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C265">
         <v>100</v>
@@ -5470,7 +5470,7 @@
         <v>274</v>
       </c>
       <c r="B266">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C266">
         <v>100</v>
@@ -5484,7 +5484,7 @@
         <v>275</v>
       </c>
       <c r="B267">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C267">
         <v>100</v>
@@ -5498,7 +5498,7 @@
         <v>276</v>
       </c>
       <c r="B268">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C268">
         <v>100</v>
@@ -5512,7 +5512,7 @@
         <v>277</v>
       </c>
       <c r="B269">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C269">
         <v>100</v>
@@ -5526,7 +5526,7 @@
         <v>278</v>
       </c>
       <c r="B270">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C270">
         <v>100</v>
@@ -5540,7 +5540,7 @@
         <v>279</v>
       </c>
       <c r="B271">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C271">
         <v>100</v>
@@ -5554,7 +5554,7 @@
         <v>280</v>
       </c>
       <c r="B272">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C272">
         <v>100</v>
@@ -5568,7 +5568,7 @@
         <v>281</v>
       </c>
       <c r="B273">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C273">
         <v>100</v>
@@ -5582,7 +5582,7 @@
         <v>282</v>
       </c>
       <c r="B274">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C274">
         <v>100</v>
@@ -5596,7 +5596,7 @@
         <v>283</v>
       </c>
       <c r="B275">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -5610,7 +5610,7 @@
         <v>284</v>
       </c>
       <c r="B276">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C276">
         <v>100</v>
@@ -5624,7 +5624,7 @@
         <v>285</v>
       </c>
       <c r="B277">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C277">
         <v>100</v>
@@ -5638,7 +5638,7 @@
         <v>182</v>
       </c>
       <c r="B278">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C278">
         <v>100</v>
@@ -5652,7 +5652,7 @@
         <v>183</v>
       </c>
       <c r="B279">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C279">
         <v>100</v>
@@ -5666,7 +5666,7 @@
         <v>180</v>
       </c>
       <c r="B280">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C280">
         <v>100</v>
@@ -5680,7 +5680,7 @@
         <v>181</v>
       </c>
       <c r="B281">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C281">
         <v>100</v>
@@ -5694,7 +5694,7 @@
         <v>185</v>
       </c>
       <c r="B282">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C282">
         <v>100</v>
@@ -5708,7 +5708,7 @@
         <v>184</v>
       </c>
       <c r="B283">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C283">
         <v>100</v>
@@ -5722,7 +5722,7 @@
         <v>413</v>
       </c>
       <c r="B284">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C284">
         <v>100</v>
@@ -5736,7 +5736,7 @@
         <v>414</v>
       </c>
       <c r="B285">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C285">
         <v>100</v>
@@ -5750,7 +5750,7 @@
         <v>162</v>
       </c>
       <c r="B286">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>100</v>
@@ -5764,7 +5764,7 @@
         <v>160</v>
       </c>
       <c r="B287">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>100</v>
@@ -5778,7 +5778,7 @@
         <v>163</v>
       </c>
       <c r="B288">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C288">
         <v>100</v>
@@ -5792,7 +5792,7 @@
         <v>164</v>
       </c>
       <c r="B289">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C289">
         <v>100</v>
@@ -5806,7 +5806,7 @@
         <v>161</v>
       </c>
       <c r="B290">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C290">
         <v>100</v>
@@ -5820,7 +5820,7 @@
         <v>165</v>
       </c>
       <c r="B291">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C291">
         <v>100</v>
@@ -5834,7 +5834,7 @@
         <v>167</v>
       </c>
       <c r="B292">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C292">
         <v>100</v>
@@ -5848,7 +5848,7 @@
         <v>166</v>
       </c>
       <c r="B293">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C293">
         <v>100</v>
@@ -5862,7 +5862,7 @@
         <v>169</v>
       </c>
       <c r="B294">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C294">
         <v>100</v>
@@ -5876,7 +5876,7 @@
         <v>168</v>
       </c>
       <c r="B295">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C295">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>415</v>
       </c>
       <c r="B296">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C296">
         <v>100</v>
@@ -5904,7 +5904,7 @@
         <v>416</v>
       </c>
       <c r="B297">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C297">
         <v>100</v>
@@ -5918,7 +5918,7 @@
         <v>417</v>
       </c>
       <c r="B298">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C298">
         <v>100</v>
@@ -5932,7 +5932,7 @@
         <v>418</v>
       </c>
       <c r="B299">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C299">
         <v>100</v>
@@ -5946,7 +5946,7 @@
         <v>419</v>
       </c>
       <c r="B300">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C300">
         <v>100</v>
@@ -5960,7 +5960,7 @@
         <v>420</v>
       </c>
       <c r="B301">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C301">
         <v>100</v>
@@ -5974,7 +5974,7 @@
         <v>421</v>
       </c>
       <c r="B302">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C302">
         <v>100</v>
@@ -5988,7 +5988,7 @@
         <v>422</v>
       </c>
       <c r="B303">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C303">
         <v>100</v>
@@ -6002,7 +6002,7 @@
         <v>423</v>
       </c>
       <c r="B304">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C304">
         <v>100</v>
@@ -6016,7 +6016,7 @@
         <v>424</v>
       </c>
       <c r="B305">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C305">
         <v>100</v>
@@ -6030,7 +6030,7 @@
         <v>149</v>
       </c>
       <c r="B306">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C306">
         <v>100</v>
@@ -6044,7 +6044,7 @@
         <v>148</v>
       </c>
       <c r="B307">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C307">
         <v>100</v>
@@ -6058,7 +6058,7 @@
         <v>145</v>
       </c>
       <c r="B308">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C308">
         <v>100</v>
@@ -6072,7 +6072,7 @@
         <v>146</v>
       </c>
       <c r="B309">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C309">
         <v>100</v>
@@ -6086,7 +6086,7 @@
         <v>147</v>
       </c>
       <c r="B310">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C310">
         <v>100</v>
@@ -6100,7 +6100,7 @@
         <v>144</v>
       </c>
       <c r="B311">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C311">
         <v>100</v>
@@ -6114,7 +6114,7 @@
         <v>141</v>
       </c>
       <c r="B312">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C312">
         <v>100</v>
@@ -6128,7 +6128,7 @@
         <v>142</v>
       </c>
       <c r="B313">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C313">
         <v>100</v>
@@ -6142,7 +6142,7 @@
         <v>143</v>
       </c>
       <c r="B314">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C314">
         <v>100</v>
@@ -6156,7 +6156,7 @@
         <v>140</v>
       </c>
       <c r="B315">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C315">
         <v>100</v>
@@ -6170,7 +6170,7 @@
         <v>132</v>
       </c>
       <c r="B316">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C316">
         <v>100</v>
@@ -6184,7 +6184,7 @@
         <v>134</v>
       </c>
       <c r="B317">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C317">
         <v>100</v>
@@ -6198,7 +6198,7 @@
         <v>130</v>
       </c>
       <c r="B318">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C318">
         <v>100</v>
@@ -6212,7 +6212,7 @@
         <v>133</v>
       </c>
       <c r="B319">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C319">
         <v>100</v>
@@ -6226,7 +6226,7 @@
         <v>131</v>
       </c>
       <c r="B320">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C320">
         <v>100</v>
@@ -6240,7 +6240,7 @@
         <v>136</v>
       </c>
       <c r="B321">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C321">
         <v>100</v>
@@ -6254,7 +6254,7 @@
         <v>139</v>
       </c>
       <c r="B322">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C322">
         <v>100</v>
@@ -6268,7 +6268,7 @@
         <v>138</v>
       </c>
       <c r="B323">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C323">
         <v>100</v>
@@ -6282,7 +6282,7 @@
         <v>135</v>
       </c>
       <c r="B324">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C324">
         <v>100</v>
@@ -6296,7 +6296,7 @@
         <v>137</v>
       </c>
       <c r="B325">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C325">
         <v>100</v>
@@ -6310,7 +6310,7 @@
         <v>128</v>
       </c>
       <c r="B326">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C326">
         <v>100</v>
@@ -6324,7 +6324,7 @@
         <v>126</v>
       </c>
       <c r="B327">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C327">
         <v>100</v>
@@ -6338,7 +6338,7 @@
         <v>129</v>
       </c>
       <c r="B328">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C328">
         <v>100</v>
@@ -6352,7 +6352,7 @@
         <v>124</v>
       </c>
       <c r="B329">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C329">
         <v>100</v>
@@ -6366,7 +6366,7 @@
         <v>125</v>
       </c>
       <c r="B330">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C330">
         <v>100</v>
@@ -6380,7 +6380,7 @@
         <v>127</v>
       </c>
       <c r="B331">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C331">
         <v>100</v>
@@ -6394,7 +6394,7 @@
         <v>118</v>
       </c>
       <c r="B332">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C332">
         <v>100</v>
@@ -6408,7 +6408,7 @@
         <v>119</v>
       </c>
       <c r="B333">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C333">
         <v>100</v>
@@ -6422,7 +6422,7 @@
         <v>121</v>
       </c>
       <c r="B334">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C334">
         <v>100</v>
@@ -6436,7 +6436,7 @@
         <v>122</v>
       </c>
       <c r="B335">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C335">
         <v>100</v>
@@ -6450,7 +6450,7 @@
         <v>123</v>
       </c>
       <c r="B336">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C336">
         <v>100</v>
@@ -6464,7 +6464,7 @@
         <v>120</v>
       </c>
       <c r="B337">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C337">
         <v>100</v>
@@ -6478,7 +6478,7 @@
         <v>64</v>
       </c>
       <c r="B338">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C338">
         <v>100</v>
@@ -6492,7 +6492,7 @@
         <v>67</v>
       </c>
       <c r="B339">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C339">
         <v>100</v>
@@ -6506,7 +6506,7 @@
         <v>68</v>
       </c>
       <c r="B340">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C340">
         <v>100</v>
@@ -6520,7 +6520,7 @@
         <v>65</v>
       </c>
       <c r="B341">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C341">
         <v>100</v>
@@ -6534,7 +6534,7 @@
         <v>69</v>
       </c>
       <c r="B342">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C342">
         <v>100</v>
@@ -6548,7 +6548,7 @@
         <v>66</v>
       </c>
       <c r="B343">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C343">
         <v>100</v>
@@ -6562,7 +6562,7 @@
         <v>75</v>
       </c>
       <c r="B344">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C344">
         <v>100</v>
@@ -6576,7 +6576,7 @@
         <v>72</v>
       </c>
       <c r="B345">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C345">
         <v>100</v>
@@ -6590,7 +6590,7 @@
         <v>71</v>
       </c>
       <c r="B346">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C346">
         <v>100</v>
@@ -6604,7 +6604,7 @@
         <v>70</v>
       </c>
       <c r="B347">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C347">
         <v>100</v>
@@ -6618,7 +6618,7 @@
         <v>73</v>
       </c>
       <c r="B348">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C348">
         <v>100</v>
@@ -6632,7 +6632,7 @@
         <v>74</v>
       </c>
       <c r="B349">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C349">
         <v>100</v>
@@ -6646,7 +6646,7 @@
         <v>97</v>
       </c>
       <c r="B350">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C350">
         <v>100</v>
@@ -6660,7 +6660,7 @@
         <v>95</v>
       </c>
       <c r="B351">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C351">
         <v>100</v>
@@ -6674,7 +6674,7 @@
         <v>94</v>
       </c>
       <c r="B352">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C352">
         <v>100</v>
@@ -6688,7 +6688,7 @@
         <v>96</v>
       </c>
       <c r="B353">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C353">
         <v>100</v>
@@ -6702,7 +6702,7 @@
         <v>93</v>
       </c>
       <c r="B354">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C354">
         <v>100</v>
@@ -6716,7 +6716,7 @@
         <v>116</v>
       </c>
       <c r="B355">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C355">
         <v>100</v>
@@ -6730,7 +6730,7 @@
         <v>114</v>
       </c>
       <c r="B356">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C356">
         <v>100</v>
@@ -6744,7 +6744,7 @@
         <v>115</v>
       </c>
       <c r="B357">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C357">
         <v>100</v>
@@ -6758,7 +6758,7 @@
         <v>113</v>
       </c>
       <c r="B358">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C358">
         <v>100</v>
@@ -6772,7 +6772,7 @@
         <v>117</v>
       </c>
       <c r="B359">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C359">
         <v>100</v>
@@ -6786,7 +6786,7 @@
         <v>102</v>
       </c>
       <c r="B360">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C360">
         <v>100</v>
@@ -6800,7 +6800,7 @@
         <v>99</v>
       </c>
       <c r="B361">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C361">
         <v>100</v>
@@ -6814,7 +6814,7 @@
         <v>101</v>
       </c>
       <c r="B362">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C362">
         <v>100</v>
@@ -6828,7 +6828,7 @@
         <v>100</v>
       </c>
       <c r="B363">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C363">
         <v>100</v>
@@ -6842,7 +6842,7 @@
         <v>98</v>
       </c>
       <c r="B364">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C364">
         <v>100</v>
@@ -6856,7 +6856,7 @@
         <v>89</v>
       </c>
       <c r="B365">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C365">
         <v>100</v>
@@ -6870,7 +6870,7 @@
         <v>90</v>
       </c>
       <c r="B366">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C366">
         <v>100</v>
@@ -6884,7 +6884,7 @@
         <v>92</v>
       </c>
       <c r="B367">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C367">
         <v>100</v>
@@ -6898,7 +6898,7 @@
         <v>91</v>
       </c>
       <c r="B368">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C368">
         <v>100</v>
@@ -6912,7 +6912,7 @@
         <v>88</v>
       </c>
       <c r="B369">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C369">
         <v>100</v>
@@ -6926,7 +6926,7 @@
         <v>109</v>
       </c>
       <c r="B370">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C370">
         <v>100</v>
@@ -6940,7 +6940,7 @@
         <v>110</v>
       </c>
       <c r="B371">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C371">
         <v>100</v>
@@ -6954,7 +6954,7 @@
         <v>111</v>
       </c>
       <c r="B372">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C372">
         <v>100</v>
@@ -6968,7 +6968,7 @@
         <v>112</v>
       </c>
       <c r="B373">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C373">
         <v>100</v>
@@ -6982,7 +6982,7 @@
         <v>108</v>
       </c>
       <c r="B374">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C374">
         <v>100</v>
@@ -6996,7 +6996,7 @@
         <v>106</v>
       </c>
       <c r="B375">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C375">
         <v>100</v>
@@ -7010,7 +7010,7 @@
         <v>103</v>
       </c>
       <c r="B376">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C376">
         <v>100</v>
@@ -7024,7 +7024,7 @@
         <v>107</v>
       </c>
       <c r="B377">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C377">
         <v>100</v>
@@ -7038,7 +7038,7 @@
         <v>105</v>
       </c>
       <c r="B378">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C378">
         <v>100</v>
@@ -7052,7 +7052,7 @@
         <v>104</v>
       </c>
       <c r="B379">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C379">
         <v>100</v>
@@ -7066,7 +7066,7 @@
         <v>80</v>
       </c>
       <c r="B380">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C380">
         <v>100</v>
@@ -7080,7 +7080,7 @@
         <v>78</v>
       </c>
       <c r="B381">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C381">
         <v>100</v>
@@ -7094,7 +7094,7 @@
         <v>79</v>
       </c>
       <c r="B382">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C382">
         <v>100</v>
@@ -7108,7 +7108,7 @@
         <v>77</v>
       </c>
       <c r="B383">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C383">
         <v>100</v>
@@ -7122,7 +7122,7 @@
         <v>76</v>
       </c>
       <c r="B384">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C384">
         <v>100</v>
@@ -7136,7 +7136,7 @@
         <v>81</v>
       </c>
       <c r="B385">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C385">
         <v>100</v>
@@ -7150,7 +7150,7 @@
         <v>83</v>
       </c>
       <c r="B386">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C386">
         <v>100</v>
@@ -7164,7 +7164,7 @@
         <v>82</v>
       </c>
       <c r="B387">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C387">
         <v>100</v>
@@ -7178,7 +7178,7 @@
         <v>87</v>
       </c>
       <c r="B388">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C388">
         <v>100</v>
@@ -7192,7 +7192,7 @@
         <v>85</v>
       </c>
       <c r="B389">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C389">
         <v>100</v>
@@ -7206,7 +7206,7 @@
         <v>84</v>
       </c>
       <c r="B390">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C390">
         <v>100</v>
@@ -7220,7 +7220,7 @@
         <v>86</v>
       </c>
       <c r="B391">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C391">
         <v>100</v>
@@ -7234,7 +7234,7 @@
         <v>60</v>
       </c>
       <c r="B392">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C392">
         <v>100</v>
@@ -7248,7 +7248,7 @@
         <v>62</v>
       </c>
       <c r="B393">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C393">
         <v>100</v>
@@ -7262,7 +7262,7 @@
         <v>61</v>
       </c>
       <c r="B394">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C394">
         <v>100</v>
@@ -7276,7 +7276,7 @@
         <v>63</v>
       </c>
       <c r="B395">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C395">
         <v>100</v>
@@ -7290,7 +7290,7 @@
         <v>59</v>
       </c>
       <c r="B396">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C396">
         <v>100</v>
@@ -7304,7 +7304,7 @@
         <v>40</v>
       </c>
       <c r="B397">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C397">
         <v>100</v>
@@ -7318,7 +7318,7 @@
         <v>39</v>
       </c>
       <c r="B398">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C398">
         <v>100</v>
@@ -7332,7 +7332,7 @@
         <v>42</v>
       </c>
       <c r="B399">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C399">
         <v>100</v>
@@ -7346,7 +7346,7 @@
         <v>43</v>
       </c>
       <c r="B400">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C400">
         <v>100</v>
@@ -7360,7 +7360,7 @@
         <v>41</v>
       </c>
       <c r="B401">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C401">
         <v>100</v>
@@ -7374,7 +7374,7 @@
         <v>45</v>
       </c>
       <c r="B402">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C402">
         <v>100</v>
@@ -7388,7 +7388,7 @@
         <v>47</v>
       </c>
       <c r="B403">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C403">
         <v>100</v>
@@ -7402,7 +7402,7 @@
         <v>48</v>
       </c>
       <c r="B404">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C404">
         <v>100</v>
@@ -7416,7 +7416,7 @@
         <v>44</v>
       </c>
       <c r="B405">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C405">
         <v>100</v>
@@ -7430,7 +7430,7 @@
         <v>46</v>
       </c>
       <c r="B406">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C406">
         <v>100</v>
@@ -7444,7 +7444,7 @@
         <v>58</v>
       </c>
       <c r="B407">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C407">
         <v>100</v>
@@ -7458,7 +7458,7 @@
         <v>54</v>
       </c>
       <c r="B408">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C408">
         <v>100</v>
@@ -7472,7 +7472,7 @@
         <v>56</v>
       </c>
       <c r="B409">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C409">
         <v>100</v>
@@ -7486,7 +7486,7 @@
         <v>57</v>
       </c>
       <c r="B410">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C410">
         <v>100</v>
@@ -7500,7 +7500,7 @@
         <v>55</v>
       </c>
       <c r="B411">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C411">
         <v>100</v>
@@ -7514,7 +7514,7 @@
         <v>49</v>
       </c>
       <c r="B412">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C412">
         <v>100</v>
@@ -7528,7 +7528,7 @@
         <v>53</v>
       </c>
       <c r="B413">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C413">
         <v>100</v>
@@ -7542,7 +7542,7 @@
         <v>50</v>
       </c>
       <c r="B414">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C414">
         <v>100</v>
@@ -7556,7 +7556,7 @@
         <v>52</v>
       </c>
       <c r="B415">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C415">
         <v>100</v>
@@ -7570,7 +7570,7 @@
         <v>51</v>
       </c>
       <c r="B416">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C416">
         <v>100</v>
@@ -7584,7 +7584,7 @@
         <v>34</v>
       </c>
       <c r="B417">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C417">
         <v>100</v>
@@ -7598,7 +7598,7 @@
         <v>35</v>
       </c>
       <c r="B418">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C418">
         <v>100</v>
@@ -7612,7 +7612,7 @@
         <v>37</v>
       </c>
       <c r="B419">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C419">
         <v>100</v>
@@ -7626,7 +7626,7 @@
         <v>36</v>
       </c>
       <c r="B420">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C420">
         <v>100</v>
@@ -7640,7 +7640,7 @@
         <v>38</v>
       </c>
       <c r="B421">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C421">
         <v>100</v>
@@ -7654,7 +7654,7 @@
         <v>425</v>
       </c>
       <c r="B422">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C422">
         <v>100</v>
@@ -7668,7 +7668,7 @@
         <v>426</v>
       </c>
       <c r="B423">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C423">
         <v>100</v>
@@ -7682,7 +7682,7 @@
         <v>427</v>
       </c>
       <c r="B424">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C424">
         <v>100</v>
@@ -7696,7 +7696,7 @@
         <v>428</v>
       </c>
       <c r="B425">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C425">
         <v>100</v>
@@ -7710,7 +7710,7 @@
         <v>429</v>
       </c>
       <c r="B426">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C426">
         <v>100</v>
@@ -7724,7 +7724,7 @@
         <v>430</v>
       </c>
       <c r="B427">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C427">
         <v>100</v>
@@ -7738,7 +7738,7 @@
         <v>431</v>
       </c>
       <c r="B428">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C428">
         <v>100</v>
@@ -7752,7 +7752,7 @@
         <v>432</v>
       </c>
       <c r="B429">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C429">
         <v>100</v>
@@ -7766,7 +7766,7 @@
         <v>433</v>
       </c>
       <c r="B430">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C430">
         <v>100</v>
@@ -7780,7 +7780,7 @@
         <v>434</v>
       </c>
       <c r="B431">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C431">
         <v>100</v>
@@ -7794,7 +7794,7 @@
         <v>435</v>
       </c>
       <c r="B432">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C432">
         <v>100</v>
@@ -7808,7 +7808,7 @@
         <v>436</v>
       </c>
       <c r="B433">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C433">
         <v>100</v>
@@ -7822,7 +7822,7 @@
         <v>437</v>
       </c>
       <c r="B434">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C434">
         <v>100</v>
@@ -7836,7 +7836,7 @@
         <v>438</v>
       </c>
       <c r="B435">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C435">
         <v>100</v>
@@ -7850,7 +7850,7 @@
         <v>439</v>
       </c>
       <c r="B436">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C436">
         <v>100</v>
@@ -7864,7 +7864,7 @@
         <v>440</v>
       </c>
       <c r="B437">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C437">
         <v>100</v>
@@ -7878,7 +7878,7 @@
         <v>441</v>
       </c>
       <c r="B438">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C438">
         <v>100</v>
@@ -7892,7 +7892,7 @@
         <v>442</v>
       </c>
       <c r="B439">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C439">
         <v>100</v>
@@ -7906,7 +7906,7 @@
         <v>443</v>
       </c>
       <c r="B440">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C440">
         <v>100</v>
@@ -7920,7 +7920,7 @@
         <v>444</v>
       </c>
       <c r="B441">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C441">
         <v>100</v>
@@ -7934,7 +7934,7 @@
         <v>445</v>
       </c>
       <c r="B442">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C442">
         <v>100</v>
@@ -7948,7 +7948,7 @@
         <v>446</v>
       </c>
       <c r="B443">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C443">
         <v>100</v>
@@ -7962,7 +7962,7 @@
         <v>447</v>
       </c>
       <c r="B444">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C444">
         <v>100</v>
@@ -7976,7 +7976,7 @@
         <v>448</v>
       </c>
       <c r="B445">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C445">
         <v>100</v>
@@ -7990,7 +7990,7 @@
         <v>449</v>
       </c>
       <c r="B446">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C446">
         <v>100</v>
@@ -8004,7 +8004,7 @@
         <v>450</v>
       </c>
       <c r="B447">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C447">
         <v>100</v>
@@ -8018,7 +8018,7 @@
         <v>451</v>
       </c>
       <c r="B448">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C448">
         <v>100</v>
@@ -8032,7 +8032,7 @@
         <v>452</v>
       </c>
       <c r="B449">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C449">
         <v>100</v>
@@ -8046,7 +8046,7 @@
         <v>453</v>
       </c>
       <c r="B450">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C450">
         <v>100</v>
@@ -8060,7 +8060,7 @@
         <v>454</v>
       </c>
       <c r="B451">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C451">
         <v>100</v>
@@ -8074,7 +8074,7 @@
         <v>455</v>
       </c>
       <c r="B452">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C452">
         <v>100</v>
@@ -8088,7 +8088,7 @@
         <v>456</v>
       </c>
       <c r="B453">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C453">
         <v>100</v>
@@ -8102,7 +8102,7 @@
         <v>457</v>
       </c>
       <c r="B454">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C454">
         <v>100</v>
@@ -8116,7 +8116,7 @@
         <v>458</v>
       </c>
       <c r="B455">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C455">
         <v>100</v>
@@ -8130,7 +8130,7 @@
         <v>459</v>
       </c>
       <c r="B456">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C456">
         <v>100</v>
@@ -8144,7 +8144,7 @@
         <v>460</v>
       </c>
       <c r="B457">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C457">
         <v>100</v>
